--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5855026472.045132</v>
+        <v>5852360461.432209</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.92279441</v>
+        <v>33.89641603</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3759023555.223317</v>
+        <v>3760760602.198229</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.77899346</v>
+        <v>21.78203253</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2428610482.235768</v>
+        <v>2427151110.587524</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07085937</v>
+        <v>14.05787021</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2227767008.306568</v>
+        <v>2232572313.161918</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.90721444</v>
+        <v>12.93088497</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1895291894.038332</v>
+        <v>1898557085.300204</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.98092341</v>
+        <v>10.99629478</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11156449</v>
+        <v>5.10991647</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175655412.9614999</v>
+        <v>175539799.8436239</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01771059</v>
+        <v>1.01671285</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20993983</v>
+        <v>0.20987215</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17259858965.88143</v>
+        <v>17265425513.59452</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E537"/>
+  <dimension ref="A1:E545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11969,6 +11969,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="n">
+        <v>2232572313.161918</v>
+      </c>
+      <c r="D538" s="3" t="n">
+        <v>12.93088497</v>
+      </c>
+      <c r="E538" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="n">
+        <v>2427151110.587524</v>
+      </c>
+      <c r="D539" s="3" t="n">
+        <v>14.05787021</v>
+      </c>
+      <c r="E539" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D540" s="3" t="n">
+        <v>5.10991647</v>
+      </c>
+      <c r="E540" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="n">
+        <v>1898557085.300204</v>
+      </c>
+      <c r="D541" s="3" t="n">
+        <v>10.99629478</v>
+      </c>
+      <c r="E541" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="n">
+        <v>3760760602.198229</v>
+      </c>
+      <c r="D542" s="3" t="n">
+        <v>21.78203253</v>
+      </c>
+      <c r="E542" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="n">
+        <v>5852360461.432209</v>
+      </c>
+      <c r="D543" s="3" t="n">
+        <v>33.89641603</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="n">
+        <v>175539799.8436239</v>
+      </c>
+      <c r="D544" s="3" t="n">
+        <v>1.01671285</v>
+      </c>
+      <c r="E544" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D545" s="3" t="n">
+        <v>0.20987215</v>
+      </c>
+      <c r="E545" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5852360461.432209</v>
+        <v>5840489312.31881</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.89641603</v>
+        <v>33.79203693</v>
       </c>
       <c r="E2" t="n">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3760760602.198229</v>
+        <v>3766790411.772142</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.78203253</v>
+        <v>21.7939823</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2427151110.587524</v>
+        <v>2434270136.392781</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.05787021</v>
+        <v>14.08425595</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2232572313.161918</v>
+        <v>2250305853.544676</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.93088497</v>
+        <v>13.01987119</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1898557085.300204</v>
+        <v>1897288253.169874</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99629478</v>
+        <v>10.97737386</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882272501.5836612</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10991647</v>
+        <v>5.10467246</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175539799.8436239</v>
+        <v>175974305.9717959</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01671285</v>
+        <v>1.01815617</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20987215</v>
+        <v>0.20965114</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17265425513.59452</v>
+        <v>17283626094.00661</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E545"/>
+  <dimension ref="A1:E553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12137,6 +12137,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="n">
+        <v>2250305853.544676</v>
+      </c>
+      <c r="D546" s="3" t="n">
+        <v>13.01987119</v>
+      </c>
+      <c r="E546" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="n">
+        <v>2434270136.392781</v>
+      </c>
+      <c r="D547" s="3" t="n">
+        <v>14.08425595</v>
+      </c>
+      <c r="E547" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="n">
+        <v>882272501.5836612</v>
+      </c>
+      <c r="D548" s="3" t="n">
+        <v>5.10467246</v>
+      </c>
+      <c r="E548" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="n">
+        <v>1897288253.169874</v>
+      </c>
+      <c r="D549" s="3" t="n">
+        <v>10.97737386</v>
+      </c>
+      <c r="E549" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="n">
+        <v>3766790411.772142</v>
+      </c>
+      <c r="D550" s="3" t="n">
+        <v>21.7939823</v>
+      </c>
+      <c r="E550" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="n">
+        <v>5840489312.31881</v>
+      </c>
+      <c r="D551" s="3" t="n">
+        <v>33.79203693</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="n">
+        <v>175974305.9717959</v>
+      </c>
+      <c r="D552" s="3" t="n">
+        <v>1.01815617</v>
+      </c>
+      <c r="E552" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D553" s="3" t="n">
+        <v>0.20965114</v>
+      </c>
+      <c r="E553" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5840489312.31881</v>
+        <v>5824061451.592879</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.79203693</v>
+        <v>33.68454717</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3766790411.772142</v>
+        <v>3765711031.9978</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.7939823</v>
+        <v>21.77969308</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2434270136.392781</v>
+        <v>2438820685.651473</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.08425595</v>
+        <v>14.10537493</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2250305853.544676</v>
+        <v>2269438459.781209</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13.01987119</v>
+        <v>13.1257212</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1897288253.169874</v>
+        <v>1897629487.769492</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.97737386</v>
+        <v>10.97529456</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882272501.5836612</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10467246</v>
+        <v>5.10265084</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175974305.9717959</v>
+        <v>175864379.5590539</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01815617</v>
+        <v>1.01714449</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20965114</v>
+        <v>0.20957374</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17283626094.00661</v>
+        <v>17290009637.42272</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E553"/>
+  <dimension ref="A1:E561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12305,6 +12305,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="n">
+        <v>2269438459.781209</v>
+      </c>
+      <c r="D554" s="3" t="n">
+        <v>13.1257212</v>
+      </c>
+      <c r="E554" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="n">
+        <v>2438820685.651473</v>
+      </c>
+      <c r="D555" s="3" t="n">
+        <v>14.10537493</v>
+      </c>
+      <c r="E555" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D556" s="3" t="n">
+        <v>5.10265084</v>
+      </c>
+      <c r="E556" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="n">
+        <v>1897629487.769492</v>
+      </c>
+      <c r="D557" s="3" t="n">
+        <v>10.97529456</v>
+      </c>
+      <c r="E557" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="n">
+        <v>3765711031.9978</v>
+      </c>
+      <c r="D558" s="3" t="n">
+        <v>21.77969308</v>
+      </c>
+      <c r="E558" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="n">
+        <v>5824061451.592879</v>
+      </c>
+      <c r="D559" s="3" t="n">
+        <v>33.68454717</v>
+      </c>
+      <c r="E559" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="n">
+        <v>175864379.5590539</v>
+      </c>
+      <c r="D560" s="3" t="n">
+        <v>1.01714449</v>
+      </c>
+      <c r="E560" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D561" s="3" t="n">
+        <v>0.20957374</v>
+      </c>
+      <c r="E561" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5824061451.592879</v>
+        <v>5819399623.178451</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.68454717</v>
+        <v>33.61208596</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3765711031.9978</v>
+        <v>3763414783.13416</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.77969308</v>
+        <v>21.73698824</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2438820685.651473</v>
+        <v>2439531990.331105</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.10537493</v>
+        <v>14.09041555</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2269438459.781209</v>
+        <v>2298237474.485224</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13.1257212</v>
+        <v>13.27431703</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1897629487.769492</v>
+        <v>1898678200.950089</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.97529456</v>
+        <v>10.96651528</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882273066.0167042</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10265084</v>
+        <v>5.09589306</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175864379.5590539</v>
+        <v>175643622.7151769</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01714449</v>
+        <v>1.01449444</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20957374</v>
+        <v>0.20929043</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17290009637.42272</v>
+        <v>17313414080.06378</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E561"/>
+  <dimension ref="A1:E569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12473,6 +12473,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="n">
+        <v>2298237474.485224</v>
+      </c>
+      <c r="D562" s="3" t="n">
+        <v>13.27431703</v>
+      </c>
+      <c r="E562" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="n">
+        <v>2439531990.331105</v>
+      </c>
+      <c r="D563" s="3" t="n">
+        <v>14.09041555</v>
+      </c>
+      <c r="E563" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="n">
+        <v>882273066.0167042</v>
+      </c>
+      <c r="D564" s="3" t="n">
+        <v>5.09589306</v>
+      </c>
+      <c r="E564" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="n">
+        <v>1898678200.950089</v>
+      </c>
+      <c r="D565" s="3" t="n">
+        <v>10.96651528</v>
+      </c>
+      <c r="E565" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="n">
+        <v>3763414783.13416</v>
+      </c>
+      <c r="D566" s="3" t="n">
+        <v>21.73698824</v>
+      </c>
+      <c r="E566" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="n">
+        <v>5819399623.178451</v>
+      </c>
+      <c r="D567" s="3" t="n">
+        <v>33.61208596</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="n">
+        <v>175643622.7151769</v>
+      </c>
+      <c r="D568" s="3" t="n">
+        <v>1.01449444</v>
+      </c>
+      <c r="E568" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D569" s="3" t="n">
+        <v>0.20929043</v>
+      </c>
+      <c r="E569" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5819399623.178451</v>
+        <v>5845372964.774499</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.61208596</v>
+        <v>34.04382064</v>
       </c>
       <c r="E2" t="n">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3763414783.13416</v>
+        <v>3764641174.781969</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.73698824</v>
+        <v>21.92550753</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2439531990.331105</v>
+        <v>2439948168.858035</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.09041555</v>
+        <v>14.21041195</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2298237474.485224</v>
+        <v>2123241977.993016</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13.27431703</v>
+        <v>12.36589513</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1898678200.950089</v>
+        <v>1902882553.415876</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96651528</v>
+        <v>11.08250795</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882273066.0167042</v>
+        <v>882263765.4358991</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.09589306</v>
+        <v>5.13835979</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175643622.7151769</v>
+        <v>175557890.2397359</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01449444</v>
+        <v>1.02246022</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20929043</v>
+        <v>0.21103678</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17313414080.06378</v>
+        <v>17170143814.75191</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E569"/>
+  <dimension ref="A1:E577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12641,6 +12641,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="n">
+        <v>2123241977.993016</v>
+      </c>
+      <c r="D570" s="3" t="n">
+        <v>12.36589513</v>
+      </c>
+      <c r="E570" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="n">
+        <v>2439948168.858035</v>
+      </c>
+      <c r="D571" s="3" t="n">
+        <v>14.21041195</v>
+      </c>
+      <c r="E571" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="n">
+        <v>882263765.4358991</v>
+      </c>
+      <c r="D572" s="3" t="n">
+        <v>5.13835979</v>
+      </c>
+      <c r="E572" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="n">
+        <v>1902882553.415876</v>
+      </c>
+      <c r="D573" s="3" t="n">
+        <v>11.08250795</v>
+      </c>
+      <c r="E573" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="n">
+        <v>3764641174.781969</v>
+      </c>
+      <c r="D574" s="3" t="n">
+        <v>21.92550753</v>
+      </c>
+      <c r="E574" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="n">
+        <v>5845372964.774499</v>
+      </c>
+      <c r="D575" s="3" t="n">
+        <v>34.04382064</v>
+      </c>
+      <c r="E575" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="n">
+        <v>175557890.2397359</v>
+      </c>
+      <c r="D576" s="3" t="n">
+        <v>1.02246022</v>
+      </c>
+      <c r="E576" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D577" s="3" t="n">
+        <v>0.21103678</v>
+      </c>
+      <c r="E577" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5845372964.774499</v>
+        <v>5832517416.250854</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04382064</v>
+        <v>33.97159406</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3764641174.781969</v>
+        <v>3770669976.605672</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.92550753</v>
+        <v>21.96232958</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2439948168.858035</v>
+        <v>2442101661.20067</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.21041195</v>
+        <v>14.22406148</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2123241977.993016</v>
+        <v>2125082939.554193</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.36589513</v>
+        <v>12.37758069</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1902882553.415876</v>
+        <v>1904229689.53201</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.08250795</v>
+        <v>11.09121729</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882263765.4358991</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13835979</v>
+        <v>5.13867284</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175557890.2397359</v>
+        <v>175721167.3866809</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02246022</v>
+        <v>1.02349084</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21103678</v>
+        <v>0.21105322</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17170143814.75191</v>
+        <v>17168806991.60089</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E577"/>
+  <dimension ref="A1:E585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12809,6 +12809,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="n">
+        <v>2125082939.554193</v>
+      </c>
+      <c r="D578" s="3" t="n">
+        <v>12.37758069</v>
+      </c>
+      <c r="E578" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="n">
+        <v>2442101661.20067</v>
+      </c>
+      <c r="D579" s="3" t="n">
+        <v>14.22406148</v>
+      </c>
+      <c r="E579" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D580" s="3" t="n">
+        <v>5.13867284</v>
+      </c>
+      <c r="E580" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="n">
+        <v>1904229689.53201</v>
+      </c>
+      <c r="D581" s="3" t="n">
+        <v>11.09121729</v>
+      </c>
+      <c r="E581" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="n">
+        <v>3770669976.605672</v>
+      </c>
+      <c r="D582" s="3" t="n">
+        <v>21.96232958</v>
+      </c>
+      <c r="E582" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="n">
+        <v>5832517416.250854</v>
+      </c>
+      <c r="D583" s="3" t="n">
+        <v>33.97159406</v>
+      </c>
+      <c r="E583" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="n">
+        <v>175721167.3866809</v>
+      </c>
+      <c r="D584" s="3" t="n">
+        <v>1.02349084</v>
+      </c>
+      <c r="E584" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D585" s="3" t="n">
+        <v>0.21105322</v>
+      </c>
+      <c r="E585" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5832517416.250854</v>
+        <v>5842391706.694088</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.97159406</v>
+        <v>34.02170866</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3770669976.605672</v>
+        <v>3764748952.751892</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96232958</v>
+        <v>21.92307508</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2442101661.20067</v>
+        <v>2439298917.100468</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.22406148</v>
+        <v>14.2046479</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2125082939.554193</v>
+        <v>2124733313.686145</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.37758069</v>
+        <v>12.37285369</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1904229689.53201</v>
+        <v>1907273760.706789</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.09121729</v>
+        <v>11.1065323</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882263654.3500812</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13867284</v>
+        <v>5.137642</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175721167.3866809</v>
+        <v>175594898.9114849</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02349084</v>
+        <v>1.02253303</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21105322</v>
+        <v>0.21100733</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17168806991.60089</v>
+        <v>17172540523.45382</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E585"/>
+  <dimension ref="A1:E593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12977,6 +12977,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="n">
+        <v>2124733313.686145</v>
+      </c>
+      <c r="D586" s="3" t="n">
+        <v>12.37285369</v>
+      </c>
+      <c r="E586" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="n">
+        <v>2439298917.100468</v>
+      </c>
+      <c r="D587" s="3" t="n">
+        <v>14.2046479</v>
+      </c>
+      <c r="E587" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="n">
+        <v>882263654.3500812</v>
+      </c>
+      <c r="D588" s="3" t="n">
+        <v>5.137642</v>
+      </c>
+      <c r="E588" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="n">
+        <v>1907273760.706789</v>
+      </c>
+      <c r="D589" s="3" t="n">
+        <v>11.1065323</v>
+      </c>
+      <c r="E589" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="n">
+        <v>3764748952.751892</v>
+      </c>
+      <c r="D590" s="3" t="n">
+        <v>21.92307508</v>
+      </c>
+      <c r="E590" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="n">
+        <v>5842391706.694088</v>
+      </c>
+      <c r="D591" s="3" t="n">
+        <v>34.02170866</v>
+      </c>
+      <c r="E591" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="n">
+        <v>175594898.9114849</v>
+      </c>
+      <c r="D592" s="3" t="n">
+        <v>1.02253303</v>
+      </c>
+      <c r="E592" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D593" s="3" t="n">
+        <v>0.21100733</v>
+      </c>
+      <c r="E593" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5842391706.694088</v>
+        <v>5879315165.893829</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.02170866</v>
+        <v>34.1274724</v>
       </c>
       <c r="E2" t="n">
         <v>1220</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3764748952.751892</v>
+        <v>3773083548.412453</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.92307508</v>
+        <v>21.9014972</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2439298917.100468</v>
+        <v>2438456117.600769</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.2046479</v>
+        <v>14.15442811</v>
       </c>
       <c r="E4" t="n">
         <v>303</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2124733313.686145</v>
+        <v>2124611306.199491</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.37285369</v>
+        <v>12.33266319</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1907273760.706789</v>
+        <v>1917867378.187407</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.1065323</v>
+        <v>11.13258333</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882263654.3500812</v>
+        <v>882262600.4448001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.137642</v>
+        <v>5.12124145</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175594898.9114849</v>
+        <v>175682798.8753289</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02253303</v>
+        <v>1.01978031</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21100733</v>
+        <v>0.210334</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17172540523.45382</v>
+        <v>17227514234.86695</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E593"/>
+  <dimension ref="A1:E601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13145,6 +13145,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="n">
+        <v>2124611306.199491</v>
+      </c>
+      <c r="D594" s="3" t="n">
+        <v>12.33266319</v>
+      </c>
+      <c r="E594" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="n">
+        <v>2438456117.600769</v>
+      </c>
+      <c r="D595" s="3" t="n">
+        <v>14.15442811</v>
+      </c>
+      <c r="E595" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="n">
+        <v>882262600.4448001</v>
+      </c>
+      <c r="D596" s="3" t="n">
+        <v>5.12124145</v>
+      </c>
+      <c r="E596" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="n">
+        <v>1917867378.187407</v>
+      </c>
+      <c r="D597" s="3" t="n">
+        <v>11.13258333</v>
+      </c>
+      <c r="E597" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="n">
+        <v>3773083548.412453</v>
+      </c>
+      <c r="D598" s="3" t="n">
+        <v>21.9014972</v>
+      </c>
+      <c r="E598" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="n">
+        <v>5879315165.893829</v>
+      </c>
+      <c r="D599" s="3" t="n">
+        <v>34.1274724</v>
+      </c>
+      <c r="E599" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="n">
+        <v>175682798.8753289</v>
+      </c>
+      <c r="D600" s="3" t="n">
+        <v>1.01978031</v>
+      </c>
+      <c r="E600" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D601" s="3" t="n">
+        <v>0.210334</v>
+      </c>
+      <c r="E601" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5879315165.893829</v>
+        <v>5836473142.944521</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.1274724</v>
+        <v>33.95269572</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3773083548.412453</v>
+        <v>3771914083.47483</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9014972</v>
+        <v>21.94247245</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2438456117.600769</v>
+        <v>2446459967.443396</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.15442811</v>
+        <v>14.23186723</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2124611306.199491</v>
+        <v>2125796411.882033</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.33266319</v>
+        <v>12.36646121</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1917867378.187407</v>
+        <v>1915260651.67699</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.13258333</v>
+        <v>11.14170502</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882262600.4448001</v>
+        <v>882249324.2356611</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12124145</v>
+        <v>5.13233628</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175682798.8753289</v>
+        <v>175625087.5616869</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01978031</v>
+        <v>1.02166925</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.210334</v>
+        <v>0.21079284</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17227514234.86695</v>
+        <v>17190013988.47199</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E601"/>
+  <dimension ref="A1:E609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13313,6 +13313,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="n">
+        <v>2125796411.882033</v>
+      </c>
+      <c r="D602" s="3" t="n">
+        <v>12.36646121</v>
+      </c>
+      <c r="E602" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="n">
+        <v>2446459967.443396</v>
+      </c>
+      <c r="D603" s="3" t="n">
+        <v>14.23186723</v>
+      </c>
+      <c r="E603" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="n">
+        <v>882249324.2356611</v>
+      </c>
+      <c r="D604" s="3" t="n">
+        <v>5.13233628</v>
+      </c>
+      <c r="E604" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="n">
+        <v>1915260651.67699</v>
+      </c>
+      <c r="D605" s="3" t="n">
+        <v>11.14170502</v>
+      </c>
+      <c r="E605" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="n">
+        <v>3771914083.47483</v>
+      </c>
+      <c r="D606" s="3" t="n">
+        <v>21.94247245</v>
+      </c>
+      <c r="E606" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="n">
+        <v>5836473142.944521</v>
+      </c>
+      <c r="D607" s="3" t="n">
+        <v>33.95269572</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="n">
+        <v>175625087.5616869</v>
+      </c>
+      <c r="D608" s="3" t="n">
+        <v>1.02166925</v>
+      </c>
+      <c r="E608" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D609" s="3" t="n">
+        <v>0.21079284</v>
+      </c>
+      <c r="E609" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5836473142.944521</v>
+        <v>5821608311.956497</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.95269572</v>
+        <v>33.94350542</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3771914083.47483</v>
+        <v>3775051662.664454</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.94247245</v>
+        <v>22.01083956</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2446459967.443396</v>
+        <v>2441575504.88033</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.23186723</v>
+        <v>14.23586523</v>
       </c>
       <c r="E4" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2125796411.882033</v>
+        <v>2128499933.24434</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.36646121</v>
+        <v>12.41044487</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1915260651.67699</v>
+        <v>1889842793.120651</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.14170502</v>
+        <v>11.01892907</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882249324.2356611</v>
+        <v>882261470.6191442</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13233628</v>
+        <v>5.14411919</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175625087.5616869</v>
+        <v>175800379.1862989</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02166925</v>
+        <v>1.02502278</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21079284</v>
+        <v>0.21127388</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17190013988.47199</v>
+        <v>17150875374.92459</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E609"/>
+  <dimension ref="A1:E617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13481,6 +13481,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="n">
+        <v>2128499933.24434</v>
+      </c>
+      <c r="D610" s="3" t="n">
+        <v>12.41044487</v>
+      </c>
+      <c r="E610" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="n">
+        <v>2441575504.88033</v>
+      </c>
+      <c r="D611" s="3" t="n">
+        <v>14.23586523</v>
+      </c>
+      <c r="E611" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="n">
+        <v>882261470.6191442</v>
+      </c>
+      <c r="D612" s="3" t="n">
+        <v>5.14411919</v>
+      </c>
+      <c r="E612" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="n">
+        <v>1889842793.120651</v>
+      </c>
+      <c r="D613" s="3" t="n">
+        <v>11.01892907</v>
+      </c>
+      <c r="E613" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="n">
+        <v>3775051662.664454</v>
+      </c>
+      <c r="D614" s="3" t="n">
+        <v>22.01083956</v>
+      </c>
+      <c r="E614" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="n">
+        <v>5821608311.956497</v>
+      </c>
+      <c r="D615" s="3" t="n">
+        <v>33.94350542</v>
+      </c>
+      <c r="E615" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="n">
+        <v>175800379.1862989</v>
+      </c>
+      <c r="D616" s="3" t="n">
+        <v>1.02502278</v>
+      </c>
+      <c r="E616" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D617" s="3" t="n">
+        <v>0.21127388</v>
+      </c>
+      <c r="E617" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5821608311.956497</v>
+        <v>5817442524.627065</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94350542</v>
+        <v>33.93552337</v>
       </c>
       <c r="E2" t="n">
         <v>1219</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3775051662.664454</v>
+        <v>3769491393.17039</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01083956</v>
+        <v>21.98898618</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2441575504.88033</v>
+        <v>2442050810.5921</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.23586523</v>
+        <v>14.24548193</v>
       </c>
       <c r="E4" t="n">
         <v>304</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2128499933.24434</v>
+        <v>2131059256.623603</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.41044487</v>
+        <v>12.4313409</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1889842793.120651</v>
+        <v>1888336496.995858</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01892907</v>
+        <v>11.0154397</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882261470.6191442</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14411919</v>
+        <v>5.14651849</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175800379.1862989</v>
+        <v>175769251.0528709</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02502278</v>
+        <v>1.02533399</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21127388</v>
+        <v>0.21137545</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17150875374.92459</v>
+        <v>17142633874.1327</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E617"/>
+  <dimension ref="A1:E625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13649,6 +13649,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="n">
+        <v>2131059256.623603</v>
+      </c>
+      <c r="D618" s="3" t="n">
+        <v>12.4313409</v>
+      </c>
+      <c r="E618" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="n">
+        <v>2442050810.5921</v>
+      </c>
+      <c r="D619" s="3" t="n">
+        <v>14.24548193</v>
+      </c>
+      <c r="E619" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D620" s="3" t="n">
+        <v>5.14651849</v>
+      </c>
+      <c r="E620" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="n">
+        <v>1888336496.995858</v>
+      </c>
+      <c r="D621" s="3" t="n">
+        <v>11.0154397</v>
+      </c>
+      <c r="E621" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="n">
+        <v>3769491393.17039</v>
+      </c>
+      <c r="D622" s="3" t="n">
+        <v>21.98898618</v>
+      </c>
+      <c r="E622" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="n">
+        <v>5817442524.627065</v>
+      </c>
+      <c r="D623" s="3" t="n">
+        <v>33.93552337</v>
+      </c>
+      <c r="E623" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="n">
+        <v>175769251.0528709</v>
+      </c>
+      <c r="D624" s="3" t="n">
+        <v>1.02533399</v>
+      </c>
+      <c r="E624" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D625" s="3" t="n">
+        <v>0.21137545</v>
+      </c>
+      <c r="E625" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5817442524.627065</v>
+        <v>5842936308.639526</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.93552337</v>
+        <v>34.04313914</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3769491393.17039</v>
+        <v>3767902769.698734</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.98898618</v>
+        <v>21.95321521</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2442050810.5921</v>
+        <v>2438173030.059599</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.24548193</v>
+        <v>14.20571085</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2131059256.623603</v>
+        <v>2133059869.266669</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4313409</v>
+        <v>12.4280071</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1888336496.995858</v>
+        <v>1886449224.155439</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.0154397</v>
+        <v>10.99116096</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14651849</v>
+        <v>5.14031265</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175769251.0528709</v>
+        <v>176324642.5035209</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02533399</v>
+        <v>1.02733352</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21137545</v>
+        <v>0.21112057</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17142633874.1327</v>
+        <v>17163329985.3943</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E625"/>
+  <dimension ref="A1:E633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13817,6 +13817,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="n">
+        <v>2133059869.266669</v>
+      </c>
+      <c r="D626" s="3" t="n">
+        <v>12.4280071</v>
+      </c>
+      <c r="E626" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="n">
+        <v>2438173030.059599</v>
+      </c>
+      <c r="D627" s="3" t="n">
+        <v>14.20571085</v>
+      </c>
+      <c r="E627" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D628" s="3" t="n">
+        <v>5.14031265</v>
+      </c>
+      <c r="E628" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="n">
+        <v>1886449224.155439</v>
+      </c>
+      <c r="D629" s="3" t="n">
+        <v>10.99116096</v>
+      </c>
+      <c r="E629" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="n">
+        <v>3767902769.698734</v>
+      </c>
+      <c r="D630" s="3" t="n">
+        <v>21.95321521</v>
+      </c>
+      <c r="E630" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="n">
+        <v>5842936308.639526</v>
+      </c>
+      <c r="D631" s="3" t="n">
+        <v>34.04313914</v>
+      </c>
+      <c r="E631" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="n">
+        <v>176324642.5035209</v>
+      </c>
+      <c r="D632" s="3" t="n">
+        <v>1.02733352</v>
+      </c>
+      <c r="E632" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D633" s="3" t="n">
+        <v>0.21112057</v>
+      </c>
+      <c r="E633" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5842936308.639526</v>
+        <v>5825561071.772702</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04313914</v>
+        <v>33.97273267</v>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3767902769.698734</v>
+        <v>3763448842.447484</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.95321521</v>
+        <v>21.94718069</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2438173030.059599</v>
+        <v>2439903873.87885</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.20571085</v>
+        <v>14.22870708</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2133059869.266669</v>
+        <v>2131875546.65461</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4280071</v>
+        <v>12.43238843</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1886449224.155439</v>
+        <v>1892796795.724778</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99116096</v>
+        <v>11.03816075</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882261450.0091442</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14031265</v>
+        <v>5.14505505</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176324642.5035209</v>
+        <v>175672411.8796019</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02733352</v>
+        <v>1.02446302</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21112057</v>
+        <v>0.21131232</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17163329985.3943</v>
+        <v>17147755311.62004</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E633"/>
+  <dimension ref="A1:E641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13985,6 +13985,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="n">
+        <v>2131875546.65461</v>
+      </c>
+      <c r="D634" s="3" t="n">
+        <v>12.43238843</v>
+      </c>
+      <c r="E634" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="n">
+        <v>2439903873.87885</v>
+      </c>
+      <c r="D635" s="3" t="n">
+        <v>14.22870708</v>
+      </c>
+      <c r="E635" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="n">
+        <v>882261450.0091442</v>
+      </c>
+      <c r="D636" s="3" t="n">
+        <v>5.14505505</v>
+      </c>
+      <c r="E636" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="n">
+        <v>1892796795.724778</v>
+      </c>
+      <c r="D637" s="3" t="n">
+        <v>11.03816075</v>
+      </c>
+      <c r="E637" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="n">
+        <v>3763448842.447484</v>
+      </c>
+      <c r="D638" s="3" t="n">
+        <v>21.94718069</v>
+      </c>
+      <c r="E638" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="n">
+        <v>5825561071.772702</v>
+      </c>
+      <c r="D639" s="3" t="n">
+        <v>33.97273267</v>
+      </c>
+      <c r="E639" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="n">
+        <v>175672411.8796019</v>
+      </c>
+      <c r="D640" s="3" t="n">
+        <v>1.02446302</v>
+      </c>
+      <c r="E640" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D641" s="3" t="n">
+        <v>0.21131232</v>
+      </c>
+      <c r="E641" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5825561071.772702</v>
+        <v>5831265120.000476</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.97273267</v>
+        <v>33.98316841</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3763448842.447484</v>
+        <v>3769685366.297195</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.94718069</v>
+        <v>21.96879236</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2439903873.87885</v>
+        <v>2437417834.002582</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.22870708</v>
+        <v>14.20466726</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2131875546.65461</v>
+        <v>2132114090.879446</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.43238843</v>
+        <v>12.42543268</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892796795.724778</v>
+        <v>1894392077.946652</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.03816075</v>
+        <v>11.04004769</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882261450.0091442</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14505505</v>
+        <v>5.14152755</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175672411.8796019</v>
+        <v>175915779.2880239</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02446302</v>
+        <v>1.02519358</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21131232</v>
+        <v>0.21117046</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17147755311.62004</v>
+        <v>17159274409.48519</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E641"/>
+  <dimension ref="A1:E649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14153,6 +14153,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="n">
+        <v>2132114090.879446</v>
+      </c>
+      <c r="D642" s="3" t="n">
+        <v>12.42543268</v>
+      </c>
+      <c r="E642" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="n">
+        <v>2437417834.002582</v>
+      </c>
+      <c r="D643" s="3" t="n">
+        <v>14.20466726</v>
+      </c>
+      <c r="E643" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D644" s="3" t="n">
+        <v>5.14152755</v>
+      </c>
+      <c r="E644" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="n">
+        <v>1894392077.946652</v>
+      </c>
+      <c r="D645" s="3" t="n">
+        <v>11.04004769</v>
+      </c>
+      <c r="E645" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="n">
+        <v>3769685366.297195</v>
+      </c>
+      <c r="D646" s="3" t="n">
+        <v>21.96879236</v>
+      </c>
+      <c r="E646" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="n">
+        <v>5831265120.000476</v>
+      </c>
+      <c r="D647" s="3" t="n">
+        <v>33.98316841</v>
+      </c>
+      <c r="E647" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="n">
+        <v>175915779.2880239</v>
+      </c>
+      <c r="D648" s="3" t="n">
+        <v>1.02519358</v>
+      </c>
+      <c r="E648" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D649" s="3" t="n">
+        <v>0.21117046</v>
+      </c>
+      <c r="E649" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5831265120.000476</v>
+        <v>5888979221.43152</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.98316841</v>
+        <v>34.2235438</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3769685366.297195</v>
+        <v>3762722013.105228</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96879236</v>
+        <v>21.86689353</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2437417834.002582</v>
+        <v>2436622506.267309</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.20466726</v>
+        <v>14.16032455</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2132114090.879446</v>
+        <v>2132338866.142641</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.42543268</v>
+        <v>12.39199356</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1894392077.946652</v>
+        <v>1892561681.69333</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.04004769</v>
+        <v>10.99853899</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14152755</v>
+        <v>5.12715023</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175915779.2880239</v>
+        <v>175683231.8046589</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02519358</v>
+        <v>1.02097538</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21117046</v>
+        <v>0.21057996</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17159274409.48519</v>
+        <v>17207391661.5155</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E649"/>
+  <dimension ref="A1:E657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14321,6 +14321,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="n">
+        <v>2132338866.142641</v>
+      </c>
+      <c r="D650" s="3" t="n">
+        <v>12.39199356</v>
+      </c>
+      <c r="E650" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="n">
+        <v>2436622506.267309</v>
+      </c>
+      <c r="D651" s="3" t="n">
+        <v>14.16032455</v>
+      </c>
+      <c r="E651" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D652" s="3" t="n">
+        <v>5.12715023</v>
+      </c>
+      <c r="E652" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="n">
+        <v>1892561681.69333</v>
+      </c>
+      <c r="D653" s="3" t="n">
+        <v>10.99853899</v>
+      </c>
+      <c r="E653" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="n">
+        <v>3762722013.105228</v>
+      </c>
+      <c r="D654" s="3" t="n">
+        <v>21.86689353</v>
+      </c>
+      <c r="E654" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="n">
+        <v>5888979221.43152</v>
+      </c>
+      <c r="D655" s="3" t="n">
+        <v>34.2235438</v>
+      </c>
+      <c r="E655" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="n">
+        <v>175683231.8046589</v>
+      </c>
+      <c r="D656" s="3" t="n">
+        <v>1.02097538</v>
+      </c>
+      <c r="E656" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D657" s="3" t="n">
+        <v>0.21057996</v>
+      </c>
+      <c r="E657" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5888979221.43152</v>
+        <v>5836084629.523401</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.2235438</v>
+        <v>33.98135396</v>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3762722013.105228</v>
+        <v>3771397409.602923</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.86689353</v>
+        <v>21.95944686</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2436622506.267309</v>
+        <v>2440475874.789584</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.16032455</v>
+        <v>14.20998491</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2132338866.142641</v>
+        <v>2136024041.605992</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.39199356</v>
+        <v>12.43727493</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892561681.69333</v>
+        <v>1895926227.123278</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99853899</v>
+        <v>11.0392745</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882261541.5208001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12715023</v>
+        <v>5.13708139</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175683231.8046589</v>
+        <v>175968397.0663009</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02097538</v>
+        <v>1.02459864</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21057996</v>
+        <v>0.21098481</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17207391661.5155</v>
+        <v>17174373440.48515</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E657"/>
+  <dimension ref="A1:E665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14489,6 +14489,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="n">
+        <v>2136024041.605992</v>
+      </c>
+      <c r="D658" s="3" t="n">
+        <v>12.43727493</v>
+      </c>
+      <c r="E658" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="n">
+        <v>2440475874.789584</v>
+      </c>
+      <c r="D659" s="3" t="n">
+        <v>14.20998491</v>
+      </c>
+      <c r="E659" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="n">
+        <v>882261541.5208001</v>
+      </c>
+      <c r="D660" s="3" t="n">
+        <v>5.13708139</v>
+      </c>
+      <c r="E660" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="n">
+        <v>1895926227.123278</v>
+      </c>
+      <c r="D661" s="3" t="n">
+        <v>11.0392745</v>
+      </c>
+      <c r="E661" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="n">
+        <v>3771397409.602923</v>
+      </c>
+      <c r="D662" s="3" t="n">
+        <v>21.95944686</v>
+      </c>
+      <c r="E662" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="n">
+        <v>5836084629.523401</v>
+      </c>
+      <c r="D663" s="3" t="n">
+        <v>33.98135396</v>
+      </c>
+      <c r="E663" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="n">
+        <v>175968397.0663009</v>
+      </c>
+      <c r="D664" s="3" t="n">
+        <v>1.02459864</v>
+      </c>
+      <c r="E664" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D665" s="3" t="n">
+        <v>0.21098481</v>
+      </c>
+      <c r="E665" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5836084629.523401</v>
+        <v>5824310357.549273</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.98135396</v>
+        <v>33.94665262</v>
       </c>
       <c r="E2" t="n">
         <v>1218</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3771397409.602923</v>
+        <v>3759251101.971066</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.95944686</v>
+        <v>21.9105754</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2440475874.789584</v>
+        <v>2444841023.513452</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.20998491</v>
+        <v>14.24961306</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2136024041.605992</v>
+        <v>2135792078.415958</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.43727493</v>
+        <v>12.44833934</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1895926227.123278</v>
+        <v>1898370777.374102</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.0392745</v>
+        <v>11.06454316</v>
       </c>
       <c r="E6" t="n">
         <v>130</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882261541.5208001</v>
+        <v>882261608.1761912</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13708139</v>
+        <v>5.14221023</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175968397.0663009</v>
+        <v>176182728.7756139</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02459864</v>
+        <v>1.02687074</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21098481</v>
+        <v>0.21119544</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17174373440.48515</v>
+        <v>17157244995.02853</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E665"/>
+  <dimension ref="A1:E673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14657,6 +14657,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="n">
+        <v>2135792078.415958</v>
+      </c>
+      <c r="D666" s="3" t="n">
+        <v>12.44833934</v>
+      </c>
+      <c r="E666" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="n">
+        <v>2444841023.513452</v>
+      </c>
+      <c r="D667" s="3" t="n">
+        <v>14.24961306</v>
+      </c>
+      <c r="E667" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="n">
+        <v>882261608.1761912</v>
+      </c>
+      <c r="D668" s="3" t="n">
+        <v>5.14221023</v>
+      </c>
+      <c r="E668" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="n">
+        <v>1898370777.374102</v>
+      </c>
+      <c r="D669" s="3" t="n">
+        <v>11.06454316</v>
+      </c>
+      <c r="E669" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="n">
+        <v>3759251101.971066</v>
+      </c>
+      <c r="D670" s="3" t="n">
+        <v>21.9105754</v>
+      </c>
+      <c r="E670" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="n">
+        <v>5824310357.549273</v>
+      </c>
+      <c r="D671" s="3" t="n">
+        <v>33.94665262</v>
+      </c>
+      <c r="E671" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="n">
+        <v>176182728.7756139</v>
+      </c>
+      <c r="D672" s="3" t="n">
+        <v>1.02687074</v>
+      </c>
+      <c r="E672" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D673" s="3" t="n">
+        <v>0.21119544</v>
+      </c>
+      <c r="E673" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5824310357.549273</v>
+        <v>5827582666.513684</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94665262</v>
+        <v>33.94286425</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3759251101.971066</v>
+        <v>3770420460.257309</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9105754</v>
+        <v>21.9608845</v>
       </c>
       <c r="E3" t="n">
         <v>228</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2444841023.513452</v>
+        <v>2442859171.743352</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.24961306</v>
+        <v>14.22847894</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2135792078.415958</v>
+        <v>2137134962.93697</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.44833934</v>
+        <v>12.44778257</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1898370777.374102</v>
+        <v>1899132854.620122</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.06454316</v>
+        <v>11.06153484</v>
       </c>
       <c r="E6" t="n">
         <v>130</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882261608.1761912</v>
+        <v>882261077.2347641</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14221023</v>
+        <v>5.13874615</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176182728.7756139</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02687074</v>
+        <v>1.00865545</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21119544</v>
+        <v>0.21105329</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17157244995.02853</v>
+        <v>17168800555.77193</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E673"/>
+  <dimension ref="A1:E681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14825,6 +14825,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="n">
+        <v>2137134962.93697</v>
+      </c>
+      <c r="D674" s="3" t="n">
+        <v>12.44778257</v>
+      </c>
+      <c r="E674" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="n">
+        <v>2442859171.743352</v>
+      </c>
+      <c r="D675" s="3" t="n">
+        <v>14.22847894</v>
+      </c>
+      <c r="E675" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="n">
+        <v>882261077.2347641</v>
+      </c>
+      <c r="D676" s="3" t="n">
+        <v>5.13874615</v>
+      </c>
+      <c r="E676" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="n">
+        <v>1899132854.620122</v>
+      </c>
+      <c r="D677" s="3" t="n">
+        <v>11.06153484</v>
+      </c>
+      <c r="E677" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="n">
+        <v>3770420460.257309</v>
+      </c>
+      <c r="D678" s="3" t="n">
+        <v>21.9608845</v>
+      </c>
+      <c r="E678" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="n">
+        <v>5827582666.513684</v>
+      </c>
+      <c r="D679" s="3" t="n">
+        <v>33.94286425</v>
+      </c>
+      <c r="E679" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D680" s="3" t="n">
+        <v>1.00865545</v>
+      </c>
+      <c r="E680" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D681" s="3" t="n">
+        <v>0.21105329</v>
+      </c>
+      <c r="E681" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5827582666.513684</v>
+        <v>5843221912.044641</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94286425</v>
+        <v>34.09414917</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3770420460.257309</v>
+        <v>3763359642.109975</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9608845</v>
+        <v>21.95852681</v>
       </c>
       <c r="E3" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2442859171.743352</v>
+        <v>2424497396.248901</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.22847894</v>
+        <v>14.14650635</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2137134962.93697</v>
+        <v>2137071395.619096</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.44778257</v>
+        <v>12.46942732</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1899132854.620122</v>
+        <v>1878680196.227284</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.06153484</v>
+        <v>10.96176113</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882261077.2347641</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13874615</v>
+        <v>5.14776324</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00865545</v>
+        <v>1.0104394</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21105329</v>
+        <v>0.21142657</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17168800555.77193</v>
+        <v>17138488726.53356</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E681"/>
+  <dimension ref="A1:E689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14993,6 +14993,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="n">
+        <v>2137071395.619096</v>
+      </c>
+      <c r="D682" s="3" t="n">
+        <v>12.46942732</v>
+      </c>
+      <c r="E682" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="n">
+        <v>2424497396.248901</v>
+      </c>
+      <c r="D683" s="3" t="n">
+        <v>14.14650635</v>
+      </c>
+      <c r="E683" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D684" s="3" t="n">
+        <v>5.14776324</v>
+      </c>
+      <c r="E684" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="n">
+        <v>1878680196.227284</v>
+      </c>
+      <c r="D685" s="3" t="n">
+        <v>10.96176113</v>
+      </c>
+      <c r="E685" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="n">
+        <v>3763359642.109975</v>
+      </c>
+      <c r="D686" s="3" t="n">
+        <v>21.95852681</v>
+      </c>
+      <c r="E686" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="n">
+        <v>5843221912.044641</v>
+      </c>
+      <c r="D687" s="3" t="n">
+        <v>34.09414917</v>
+      </c>
+      <c r="E687" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D688" s="3" t="n">
+        <v>1.0104394</v>
+      </c>
+      <c r="E688" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D689" s="3" t="n">
+        <v>0.21142657</v>
+      </c>
+      <c r="E689" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5843221912.044641</v>
+        <v>5834908187.348917</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.09414917</v>
+        <v>34.06338144</v>
       </c>
       <c r="E2" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3763359642.109975</v>
+        <v>3761830365.302734</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.95852681</v>
+        <v>21.96104181</v>
       </c>
       <c r="E3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2424497396.248901</v>
+        <v>2423544860.965056</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.14650635</v>
+        <v>14.1483174</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2137071395.619096</v>
+        <v>2138774305.012324</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.46942732</v>
+        <v>12.48586655</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1878680196.227284</v>
+        <v>1878843121.148277</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96176113</v>
+        <v>10.9684245</v>
       </c>
       <c r="E6" t="n">
         <v>126</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882252220.6395252</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14776324</v>
+        <v>5.1504656</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0104394</v>
+        <v>1.01096595</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21142657</v>
+        <v>0.21153675</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17138488726.53356</v>
+        <v>17129562422.88256</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E689"/>
+  <dimension ref="A1:E697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15161,6 +15161,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="n">
+        <v>2138774305.012324</v>
+      </c>
+      <c r="D690" s="3" t="n">
+        <v>12.48586655</v>
+      </c>
+      <c r="E690" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="n">
+        <v>2423544860.965056</v>
+      </c>
+      <c r="D691" s="3" t="n">
+        <v>14.1483174</v>
+      </c>
+      <c r="E691" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="n">
+        <v>882252220.6395252</v>
+      </c>
+      <c r="D692" s="3" t="n">
+        <v>5.1504656</v>
+      </c>
+      <c r="E692" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="n">
+        <v>1878843121.148277</v>
+      </c>
+      <c r="D693" s="3" t="n">
+        <v>10.9684245</v>
+      </c>
+      <c r="E693" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="n">
+        <v>3761830365.302734</v>
+      </c>
+      <c r="D694" s="3" t="n">
+        <v>21.96104181</v>
+      </c>
+      <c r="E694" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="n">
+        <v>5834908187.348917</v>
+      </c>
+      <c r="D695" s="3" t="n">
+        <v>34.06338144</v>
+      </c>
+      <c r="E695" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D696" s="3" t="n">
+        <v>1.01096595</v>
+      </c>
+      <c r="E696" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D697" s="3" t="n">
+        <v>0.21153675</v>
+      </c>
+      <c r="E697" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5834908187.348917</v>
+        <v>5840571145.218137</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.06338144</v>
+        <v>34.08044894</v>
       </c>
       <c r="E2" t="n">
         <v>1224</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3761830365.302734</v>
+        <v>3766413290.110857</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96104181</v>
+        <v>21.97748347</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423544860.965056</v>
+        <v>2420637438.338618</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.1483174</v>
+        <v>14.12471633</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2138774305.012324</v>
+        <v>2139181603.91746</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48586655</v>
+        <v>12.48238702</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1878843121.148277</v>
+        <v>1879138712.528613</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.9684245</v>
+        <v>10.96500485</v>
       </c>
       <c r="E6" t="n">
         <v>126</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882252220.6395252</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1504656</v>
+        <v>5.14803008</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01096595</v>
+        <v>1.01049178</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21153675</v>
+        <v>0.21143753</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17129562422.88256</v>
+        <v>17137600374.39735</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E697"/>
+  <dimension ref="A1:E705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15329,6 +15329,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="n">
+        <v>2139181603.91746</v>
+      </c>
+      <c r="D698" s="3" t="n">
+        <v>12.48238702</v>
+      </c>
+      <c r="E698" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="n">
+        <v>2420637438.338618</v>
+      </c>
+      <c r="D699" s="3" t="n">
+        <v>14.12471633</v>
+      </c>
+      <c r="E699" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D700" s="3" t="n">
+        <v>5.14803008</v>
+      </c>
+      <c r="E700" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="n">
+        <v>1879138712.528613</v>
+      </c>
+      <c r="D701" s="3" t="n">
+        <v>10.96500485</v>
+      </c>
+      <c r="E701" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="n">
+        <v>3766413290.110857</v>
+      </c>
+      <c r="D702" s="3" t="n">
+        <v>21.97748347</v>
+      </c>
+      <c r="E702" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="n">
+        <v>5840571145.218137</v>
+      </c>
+      <c r="D703" s="3" t="n">
+        <v>34.08044894</v>
+      </c>
+      <c r="E703" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D704" s="3" t="n">
+        <v>1.01049178</v>
+      </c>
+      <c r="E704" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D705" s="3" t="n">
+        <v>0.21143753</v>
+      </c>
+      <c r="E705" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5840571145.218137</v>
+        <v>5902477650.704552</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.08044894</v>
+        <v>34.30202491</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3766413290.110857</v>
+        <v>3780866807.674415</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.97748347</v>
+        <v>21.97236399</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420637438.338618</v>
+        <v>2418614818.593271</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.12471633</v>
+        <v>14.05568825</v>
       </c>
       <c r="E4" t="n">
         <v>301</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2139181603.91746</v>
+        <v>2134809516.033541</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48238702</v>
+        <v>12.4063645</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1879138712.528613</v>
+        <v>1878939587.23301</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.96500485</v>
+        <v>10.91938612</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882256069.2584982</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14803008</v>
+        <v>5.12719767</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01049178</v>
+        <v>1.00639438</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21143753</v>
+        <v>0.21058018</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17137600374.39735</v>
+        <v>17207373811.96301</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E705"/>
+  <dimension ref="A1:E713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15497,6 +15497,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="n">
+        <v>2134809516.033541</v>
+      </c>
+      <c r="D706" s="3" t="n">
+        <v>12.4063645</v>
+      </c>
+      <c r="E706" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="n">
+        <v>2418614818.593271</v>
+      </c>
+      <c r="D707" s="3" t="n">
+        <v>14.05568825</v>
+      </c>
+      <c r="E707" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="n">
+        <v>882256069.2584982</v>
+      </c>
+      <c r="D708" s="3" t="n">
+        <v>5.12719767</v>
+      </c>
+      <c r="E708" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="n">
+        <v>1878939587.23301</v>
+      </c>
+      <c r="D709" s="3" t="n">
+        <v>10.91938612</v>
+      </c>
+      <c r="E709" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="n">
+        <v>3780866807.674415</v>
+      </c>
+      <c r="D710" s="3" t="n">
+        <v>21.97236399</v>
+      </c>
+      <c r="E710" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="n">
+        <v>5902477650.704552</v>
+      </c>
+      <c r="D711" s="3" t="n">
+        <v>34.30202491</v>
+      </c>
+      <c r="E711" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D712" s="3" t="n">
+        <v>1.00639438</v>
+      </c>
+      <c r="E712" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D713" s="3" t="n">
+        <v>0.21058018</v>
+      </c>
+      <c r="E713" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5902477650.704552</v>
+        <v>5848278033.787913</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.30202491</v>
+        <v>34.07416498</v>
       </c>
       <c r="E2" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3780866807.674415</v>
+        <v>3775305508.920911</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.97236399</v>
+        <v>21.9962837</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2418614818.593271</v>
+        <v>2421621377.719771</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.05568825</v>
+        <v>14.10923453</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2134809516.033541</v>
+        <v>2136564103.532933</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4063645</v>
+        <v>12.44838863</v>
       </c>
       <c r="E5" t="n">
         <v>45</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1878939587.23301</v>
+        <v>1889948136.639764</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.91938612</v>
+        <v>11.01151557</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882256069.2584982</v>
+        <v>882252349.6018301</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12719767</v>
+        <v>5.14031856</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00639438</v>
+        <v>1.00897407</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21058018</v>
+        <v>0.21111996</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17207373811.96301</v>
+        <v>17163378872.66885</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E713"/>
+  <dimension ref="A1:E721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15665,6 +15665,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="n">
+        <v>2136564103.532933</v>
+      </c>
+      <c r="D714" s="3" t="n">
+        <v>12.44838863</v>
+      </c>
+      <c r="E714" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="n">
+        <v>2421621377.719771</v>
+      </c>
+      <c r="D715" s="3" t="n">
+        <v>14.10923453</v>
+      </c>
+      <c r="E715" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="n">
+        <v>882252349.6018301</v>
+      </c>
+      <c r="D716" s="3" t="n">
+        <v>5.14031856</v>
+      </c>
+      <c r="E716" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="n">
+        <v>1889948136.639764</v>
+      </c>
+      <c r="D717" s="3" t="n">
+        <v>11.01151557</v>
+      </c>
+      <c r="E717" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="n">
+        <v>3775305508.920911</v>
+      </c>
+      <c r="D718" s="3" t="n">
+        <v>21.9962837</v>
+      </c>
+      <c r="E718" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="n">
+        <v>5848278033.787913</v>
+      </c>
+      <c r="D719" s="3" t="n">
+        <v>34.07416498</v>
+      </c>
+      <c r="E719" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D720" s="3" t="n">
+        <v>1.00897407</v>
+      </c>
+      <c r="E720" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D721" s="3" t="n">
+        <v>0.21111996</v>
+      </c>
+      <c r="E721" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5848278033.787913</v>
+        <v>5851827203.714178</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.07416498</v>
+        <v>34.11161265</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3775305508.920911</v>
+        <v>3766518304.042012</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.9962837</v>
+        <v>21.95587958</v>
       </c>
       <c r="E3" t="n">
         <v>229</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2421621377.719771</v>
+        <v>2422275920.460848</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.10923453</v>
+        <v>14.11998937</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2136564103.532933</v>
+        <v>2136930207.372152</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.44838863</v>
+        <v>12.45664524</v>
       </c>
       <c r="E5" t="n">
         <v>45</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1889948136.639764</v>
+        <v>1885731705.745491</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01151557</v>
+        <v>10.99235286</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882252349.6018301</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14031856</v>
+        <v>5.14282617</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00897407</v>
+        <v>1.00947032</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21111996</v>
+        <v>0.2112238</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17163378872.66885</v>
+        <v>17154941525.61834</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E721"/>
+  <dimension ref="A1:E729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15833,6 +15833,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="n">
+        <v>2136930207.372152</v>
+      </c>
+      <c r="D722" s="3" t="n">
+        <v>12.45664524</v>
+      </c>
+      <c r="E722" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="n">
+        <v>2422275920.460848</v>
+      </c>
+      <c r="D723" s="3" t="n">
+        <v>14.11998937</v>
+      </c>
+      <c r="E723" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D724" s="3" t="n">
+        <v>5.14282617</v>
+      </c>
+      <c r="E724" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="n">
+        <v>1885731705.745491</v>
+      </c>
+      <c r="D725" s="3" t="n">
+        <v>10.99235286</v>
+      </c>
+      <c r="E725" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="n">
+        <v>3766518304.042012</v>
+      </c>
+      <c r="D726" s="3" t="n">
+        <v>21.95587958</v>
+      </c>
+      <c r="E726" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="n">
+        <v>5851827203.714178</v>
+      </c>
+      <c r="D727" s="3" t="n">
+        <v>34.11161265</v>
+      </c>
+      <c r="E727" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D728" s="3" t="n">
+        <v>1.00947032</v>
+      </c>
+      <c r="E728" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D729" s="3" t="n">
+        <v>0.2112238</v>
+      </c>
+      <c r="E729" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5851827203.714178</v>
+        <v>5832187744.696218</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.11161265</v>
+        <v>34.01363015</v>
       </c>
       <c r="E2" t="n">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3766518304.042012</v>
+        <v>3774521041.854661</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.95587958</v>
+        <v>22.01320814</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2422275920.460848</v>
+        <v>2422942301.238055</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.11998937</v>
+        <v>14.1307288</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2136930207.372152</v>
+        <v>2140415644.316266</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.45664524</v>
+        <v>12.48301826</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1885731705.745491</v>
+        <v>1884894597.139369</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99235286</v>
+        <v>10.99280587</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14282617</v>
+        <v>5.14532221</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00947032</v>
+        <v>1.00996026</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2112238</v>
+        <v>0.21132632</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17154941525.61834</v>
+        <v>17146619513.52823</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E729"/>
+  <dimension ref="A1:E737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16001,6 +16001,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="n">
+        <v>2140415644.316266</v>
+      </c>
+      <c r="D730" s="3" t="n">
+        <v>12.48301826</v>
+      </c>
+      <c r="E730" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="n">
+        <v>2422942301.238055</v>
+      </c>
+      <c r="D731" s="3" t="n">
+        <v>14.1307288</v>
+      </c>
+      <c r="E731" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D732" s="3" t="n">
+        <v>5.14532221</v>
+      </c>
+      <c r="E732" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="n">
+        <v>1884894597.139369</v>
+      </c>
+      <c r="D733" s="3" t="n">
+        <v>10.99280587</v>
+      </c>
+      <c r="E733" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="n">
+        <v>3774521041.854661</v>
+      </c>
+      <c r="D734" s="3" t="n">
+        <v>22.01320814</v>
+      </c>
+      <c r="E734" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="n">
+        <v>5832187744.696218</v>
+      </c>
+      <c r="D735" s="3" t="n">
+        <v>34.01363015</v>
+      </c>
+      <c r="E735" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D736" s="3" t="n">
+        <v>1.00996026</v>
+      </c>
+      <c r="E736" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D737" s="3" t="n">
+        <v>0.21132632</v>
+      </c>
+      <c r="E737" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5832187744.696218</v>
+        <v>5837723666.047632</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.01363015</v>
+        <v>34.00363147</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3774521041.854661</v>
+        <v>3780378100.200007</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01320814</v>
+        <v>22.01998434</v>
       </c>
       <c r="E3" t="n">
         <v>230</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2422942301.238055</v>
+        <v>2423915353.778654</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.1307288</v>
+        <v>14.11884651</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2140415644.316266</v>
+        <v>2144634751.774688</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48301826</v>
+        <v>12.49209005</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1884894597.139369</v>
+        <v>1889631761.952415</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99280587</v>
+        <v>11.00674607</v>
       </c>
       <c r="E6" t="n">
         <v>126</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.14532221</v>
+        <v>5.1389318</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00996026</v>
+        <v>1.00870591</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21132632</v>
+        <v>0.21106385</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17146619513.52823</v>
+        <v>17167941818.03706</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E737"/>
+  <dimension ref="A1:E745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16169,6 +16169,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="n">
+        <v>2144634751.774688</v>
+      </c>
+      <c r="D738" s="3" t="n">
+        <v>12.49209005</v>
+      </c>
+      <c r="E738" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="n">
+        <v>2423915353.778654</v>
+      </c>
+      <c r="D739" s="3" t="n">
+        <v>14.11884651</v>
+      </c>
+      <c r="E739" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D740" s="3" t="n">
+        <v>5.1389318</v>
+      </c>
+      <c r="E740" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="n">
+        <v>1889631761.952415</v>
+      </c>
+      <c r="D741" s="3" t="n">
+        <v>11.00674607</v>
+      </c>
+      <c r="E741" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="n">
+        <v>3780378100.200007</v>
+      </c>
+      <c r="D742" s="3" t="n">
+        <v>22.01998434</v>
+      </c>
+      <c r="E742" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="n">
+        <v>5837723666.047632</v>
+      </c>
+      <c r="D743" s="3" t="n">
+        <v>34.00363147</v>
+      </c>
+      <c r="E743" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D744" s="3" t="n">
+        <v>1.00870591</v>
+      </c>
+      <c r="E744" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D745" s="3" t="n">
+        <v>0.21106385</v>
+      </c>
+      <c r="E745" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5837723666.047632</v>
+        <v>5832948313.670458</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.00363147</v>
+        <v>33.98151583</v>
       </c>
       <c r="E2" t="n">
         <v>1223</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3780378100.200007</v>
+        <v>3776591564.263817</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.01998434</v>
+        <v>22.00161893</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423915353.778654</v>
+        <v>2423841548.457971</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.11884651</v>
+        <v>14.12078515</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2144634751.774688</v>
+        <v>2145367095.019296</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.49209005</v>
+        <v>12.49845224</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1889631761.952415</v>
+        <v>1894650625.5397</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.00674607</v>
+        <v>11.03783143</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882253645.9823512</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1389318</v>
+        <v>5.13982203</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00870591</v>
+        <v>1.00887513</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21106385</v>
+        <v>0.21109926</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17167941818.03706</v>
+        <v>17165062155.39932</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E745"/>
+  <dimension ref="A1:E753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16337,6 +16337,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="n">
+        <v>2145367095.019296</v>
+      </c>
+      <c r="D746" s="3" t="n">
+        <v>12.49845224</v>
+      </c>
+      <c r="E746" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="n">
+        <v>2423841548.457971</v>
+      </c>
+      <c r="D747" s="3" t="n">
+        <v>14.12078515</v>
+      </c>
+      <c r="E747" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="n">
+        <v>882253645.9823512</v>
+      </c>
+      <c r="D748" s="3" t="n">
+        <v>5.13982203</v>
+      </c>
+      <c r="E748" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="n">
+        <v>1894650625.5397</v>
+      </c>
+      <c r="D749" s="3" t="n">
+        <v>11.03783143</v>
+      </c>
+      <c r="E749" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="n">
+        <v>3776591564.263817</v>
+      </c>
+      <c r="D750" s="3" t="n">
+        <v>22.00161893</v>
+      </c>
+      <c r="E750" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="n">
+        <v>5832948313.670458</v>
+      </c>
+      <c r="D751" s="3" t="n">
+        <v>33.98151583</v>
+      </c>
+      <c r="E751" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D752" s="3" t="n">
+        <v>1.00887513</v>
+      </c>
+      <c r="E752" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D753" s="3" t="n">
+        <v>0.21109926</v>
+      </c>
+      <c r="E753" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5832948313.670458</v>
+        <v>5840790462.572275</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.98151583</v>
+        <v>34.03896991</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3776591564.263817</v>
+        <v>3773845190.072969</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.00161893</v>
+        <v>21.99322227</v>
       </c>
       <c r="E3" t="n">
         <v>229</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423841548.457971</v>
+        <v>2422653827.695027</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.12078515</v>
+        <v>14.11874664</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2145367095.019296</v>
+        <v>2142833603.121234</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.49845224</v>
+        <v>12.4880098</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1894650625.5397</v>
+        <v>1887343758.106426</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.03783143</v>
+        <v>10.99906559</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882253645.9823512</v>
+        <v>882251929.7509222</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13982203</v>
+        <v>5.1415895</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00887513</v>
+        <v>1.00922402</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21109926</v>
+        <v>0.21117226</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17165062155.39932</v>
+        <v>17159128133.78458</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E753"/>
+  <dimension ref="A1:E761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16505,6 +16505,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="n">
+        <v>2142833603.121234</v>
+      </c>
+      <c r="D754" s="3" t="n">
+        <v>12.4880098</v>
+      </c>
+      <c r="E754" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="n">
+        <v>2422653827.695027</v>
+      </c>
+      <c r="D755" s="3" t="n">
+        <v>14.11874664</v>
+      </c>
+      <c r="E755" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="n">
+        <v>882251929.7509222</v>
+      </c>
+      <c r="D756" s="3" t="n">
+        <v>5.1415895</v>
+      </c>
+      <c r="E756" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="n">
+        <v>1887343758.106426</v>
+      </c>
+      <c r="D757" s="3" t="n">
+        <v>10.99906559</v>
+      </c>
+      <c r="E757" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="n">
+        <v>3773845190.072969</v>
+      </c>
+      <c r="D758" s="3" t="n">
+        <v>21.99322227</v>
+      </c>
+      <c r="E758" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="n">
+        <v>5840790462.572275</v>
+      </c>
+      <c r="D759" s="3" t="n">
+        <v>34.03896991</v>
+      </c>
+      <c r="E759" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D760" s="3" t="n">
+        <v>1.00922402</v>
+      </c>
+      <c r="E760" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D761" s="3" t="n">
+        <v>0.21117226</v>
+      </c>
+      <c r="E761" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5840790462.572275</v>
+        <v>5867476673.501523</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.03896991</v>
+        <v>34.14496089</v>
       </c>
       <c r="E2" t="n">
         <v>1225</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3773845190.072969</v>
+        <v>3772682509.490763</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.99322227</v>
+        <v>21.95459887</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2422653827.695027</v>
+        <v>2420812012.998322</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.11874664</v>
+        <v>14.08757735</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2142833603.121234</v>
+        <v>2143102229.072223</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.4880098</v>
+        <v>12.47148406</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1887343758.106426</v>
+        <v>1888283058.049824</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99906559</v>
+        <v>10.98859949</v>
       </c>
       <c r="E6" t="n">
         <v>126</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882251929.7509222</v>
+        <v>882253465.6823511</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1415895</v>
+        <v>5.1341508</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00922402</v>
+        <v>1.00776215</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21117226</v>
+        <v>0.21086638</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17159128133.78458</v>
+        <v>17184019311.26073</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E761"/>
+  <dimension ref="A1:E769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16673,6 +16673,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="n">
+        <v>2143102229.072223</v>
+      </c>
+      <c r="D762" s="3" t="n">
+        <v>12.47148406</v>
+      </c>
+      <c r="E762" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="n">
+        <v>2420812012.998322</v>
+      </c>
+      <c r="D763" s="3" t="n">
+        <v>14.08757735</v>
+      </c>
+      <c r="E763" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="n">
+        <v>882253465.6823511</v>
+      </c>
+      <c r="D764" s="3" t="n">
+        <v>5.1341508</v>
+      </c>
+      <c r="E764" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="n">
+        <v>1888283058.049824</v>
+      </c>
+      <c r="D765" s="3" t="n">
+        <v>10.98859949</v>
+      </c>
+      <c r="E765" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="n">
+        <v>3772682509.490763</v>
+      </c>
+      <c r="D766" s="3" t="n">
+        <v>21.95459887</v>
+      </c>
+      <c r="E766" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="n">
+        <v>5867476673.501523</v>
+      </c>
+      <c r="D767" s="3" t="n">
+        <v>34.14496089</v>
+      </c>
+      <c r="E767" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D768" s="3" t="n">
+        <v>1.00776215</v>
+      </c>
+      <c r="E768" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D769" s="3" t="n">
+        <v>0.21086638</v>
+      </c>
+      <c r="E769" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5867476673.501523</v>
+        <v>5845151223.033852</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.14496089</v>
+        <v>34.03216858</v>
       </c>
       <c r="E2" t="n">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3772682509.490763</v>
+        <v>3777956641.66401</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.95459887</v>
+        <v>21.99636116</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420812012.998322</v>
+        <v>2423826426.440224</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.08757735</v>
+        <v>14.11222164</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2143102229.072223</v>
+        <v>2144528216.007426</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.47148406</v>
+        <v>12.48606631</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1888283058.049824</v>
+        <v>1892244988.105362</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.98859949</v>
+        <v>11.01720006</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882253465.6823511</v>
+        <v>882254172.2340761</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.1341508</v>
+        <v>5.13674011</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00776215</v>
+        <v>1.00826959</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21086638</v>
+        <v>0.21097256</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17184019311.26073</v>
+        <v>17175371029.95067</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E769"/>
+  <dimension ref="A1:E777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16841,6 +16841,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="n">
+        <v>2144528216.007426</v>
+      </c>
+      <c r="D770" s="3" t="n">
+        <v>12.48606631</v>
+      </c>
+      <c r="E770" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="n">
+        <v>2423826426.440224</v>
+      </c>
+      <c r="D771" s="3" t="n">
+        <v>14.11222164</v>
+      </c>
+      <c r="E771" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="n">
+        <v>882254172.2340761</v>
+      </c>
+      <c r="D772" s="3" t="n">
+        <v>5.13674011</v>
+      </c>
+      <c r="E772" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="n">
+        <v>1892244988.105362</v>
+      </c>
+      <c r="D773" s="3" t="n">
+        <v>11.01720006</v>
+      </c>
+      <c r="E773" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="n">
+        <v>3777956641.66401</v>
+      </c>
+      <c r="D774" s="3" t="n">
+        <v>21.99636116</v>
+      </c>
+      <c r="E774" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="n">
+        <v>5845151223.033852</v>
+      </c>
+      <c r="D775" s="3" t="n">
+        <v>34.03216858</v>
+      </c>
+      <c r="E775" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D776" s="3" t="n">
+        <v>1.00826959</v>
+      </c>
+      <c r="E776" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D777" s="3" t="n">
+        <v>0.21097256</v>
+      </c>
+      <c r="E777" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5845151223.033852</v>
+        <v>5846883119.200485</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.03216858</v>
+        <v>34.04343223</v>
       </c>
       <c r="E2" t="n">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3777956641.66401</v>
+        <v>3775761716.437345</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.99636116</v>
+        <v>21.98434371</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423826426.440224</v>
+        <v>2422985972.672757</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.11222164</v>
+        <v>14.10781729</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2144528216.007426</v>
+        <v>2145939368.955519</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.48606631</v>
+        <v>12.49471556</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1892244988.105362</v>
+        <v>1891541837.66251</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01720006</v>
+        <v>11.01348788</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882254172.2340761</v>
+        <v>882254302.2840761</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13674011</v>
+        <v>5.13691893</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00826959</v>
+        <v>1.00830454</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21097256</v>
+        <v>0.21097987</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17175371029.95067</v>
+        <v>17174775679.67842</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E777"/>
+  <dimension ref="A1:E785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17009,6 +17009,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="n">
+        <v>2145939368.955519</v>
+      </c>
+      <c r="D778" s="3" t="n">
+        <v>12.49471556</v>
+      </c>
+      <c r="E778" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="n">
+        <v>2422985972.672757</v>
+      </c>
+      <c r="D779" s="3" t="n">
+        <v>14.10781729</v>
+      </c>
+      <c r="E779" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="n">
+        <v>882254302.2840761</v>
+      </c>
+      <c r="D780" s="3" t="n">
+        <v>5.13691893</v>
+      </c>
+      <c r="E780" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="n">
+        <v>1891541837.66251</v>
+      </c>
+      <c r="D781" s="3" t="n">
+        <v>11.01348788</v>
+      </c>
+      <c r="E781" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="n">
+        <v>3775761716.437345</v>
+      </c>
+      <c r="D782" s="3" t="n">
+        <v>21.98434371</v>
+      </c>
+      <c r="E782" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="n">
+        <v>5846883119.200485</v>
+      </c>
+      <c r="D783" s="3" t="n">
+        <v>34.04343223</v>
+      </c>
+      <c r="E783" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D784" s="3" t="n">
+        <v>1.00830454</v>
+      </c>
+      <c r="E784" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D785" s="3" t="n">
+        <v>0.21097987</v>
+      </c>
+      <c r="E785" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5846883119.200485</v>
+        <v>5853365972.98327</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04343223</v>
+        <v>34.05446131</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3775761716.437345</v>
+        <v>3776242138.739917</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.98434371</v>
+        <v>21.96990457</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2422985972.672757</v>
+        <v>2422867723.502769</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.10781729</v>
+        <v>14.09606977</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2145939368.955519</v>
+        <v>2151072367.818742</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.49471556</v>
+        <v>12.51478398</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1891541837.66251</v>
+        <v>1893039217.724787</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01348788</v>
+        <v>11.01356572</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882254302.2840761</v>
+        <v>882253294.3340762</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13691893</v>
+        <v>5.13288607</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00830454</v>
+        <v>1.0075141</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21097987</v>
+        <v>0.21081448</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17174775679.67842</v>
+        <v>17188250077.56929</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E785"/>
+  <dimension ref="A1:E793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17177,6 +17177,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="n">
+        <v>2151072367.818742</v>
+      </c>
+      <c r="D786" s="3" t="n">
+        <v>12.51478398</v>
+      </c>
+      <c r="E786" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="n">
+        <v>2422867723.502769</v>
+      </c>
+      <c r="D787" s="3" t="n">
+        <v>14.09606977</v>
+      </c>
+      <c r="E787" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="n">
+        <v>882253294.3340762</v>
+      </c>
+      <c r="D788" s="3" t="n">
+        <v>5.13288607</v>
+      </c>
+      <c r="E788" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="n">
+        <v>1893039217.724787</v>
+      </c>
+      <c r="D789" s="3" t="n">
+        <v>11.01356572</v>
+      </c>
+      <c r="E789" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="n">
+        <v>3776242138.739917</v>
+      </c>
+      <c r="D790" s="3" t="n">
+        <v>21.96990457</v>
+      </c>
+      <c r="E790" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="n">
+        <v>5853365972.98327</v>
+      </c>
+      <c r="D791" s="3" t="n">
+        <v>34.05446131</v>
+      </c>
+      <c r="E791" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D792" s="3" t="n">
+        <v>1.0075141</v>
+      </c>
+      <c r="E792" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D793" s="3" t="n">
+        <v>0.21081448</v>
+      </c>
+      <c r="E793" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5853365972.98327</v>
+        <v>5855018148.259865</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.05446131</v>
+        <v>34.04929225</v>
       </c>
       <c r="E2" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3776242138.739917</v>
+        <v>3781557899.770401</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96990457</v>
+        <v>21.99128454</v>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2422867723.502769</v>
+        <v>2419592769.875572</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.09606977</v>
+        <v>14.07090794</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2151072367.818742</v>
+        <v>2152957864.025059</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.51478398</v>
+        <v>12.52031841</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1893039217.724787</v>
+        <v>1894926885.15104</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01356572</v>
+        <v>11.01976419</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882253294.3340762</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13288607</v>
+        <v>5.13063277</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0075141</v>
+        <v>1.00707691</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21081448</v>
+        <v>0.210723</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17188250077.56929</v>
+        <v>17195711751.3656</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E793"/>
+  <dimension ref="A1:E801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17345,6 +17345,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="n">
+        <v>2152957864.025059</v>
+      </c>
+      <c r="D794" s="3" t="n">
+        <v>12.52031841</v>
+      </c>
+      <c r="E794" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="n">
+        <v>2419592769.875572</v>
+      </c>
+      <c r="D795" s="3" t="n">
+        <v>14.07090794</v>
+      </c>
+      <c r="E795" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D796" s="3" t="n">
+        <v>5.13063277</v>
+      </c>
+      <c r="E796" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="n">
+        <v>1894926885.15104</v>
+      </c>
+      <c r="D797" s="3" t="n">
+        <v>11.01976419</v>
+      </c>
+      <c r="E797" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="n">
+        <v>3781557899.770401</v>
+      </c>
+      <c r="D798" s="3" t="n">
+        <v>21.99128454</v>
+      </c>
+      <c r="E798" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="n">
+        <v>5855018148.259865</v>
+      </c>
+      <c r="D799" s="3" t="n">
+        <v>34.04929225</v>
+      </c>
+      <c r="E799" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D800" s="3" t="n">
+        <v>1.00707691</v>
+      </c>
+      <c r="E800" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D801" s="3" t="n">
+        <v>0.210723</v>
+      </c>
+      <c r="E801" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5855018148.259865</v>
+        <v>5832691581.540565</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04929225</v>
+        <v>33.95496456</v>
       </c>
       <c r="E2" t="n">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3781557899.770401</v>
+        <v>3779750876.72166</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.99128454</v>
+        <v>22.00378766</v>
       </c>
       <c r="E3" t="n">
         <v>230</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2419592769.875572</v>
+        <v>2418758629.186609</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07090794</v>
+        <v>14.08078284</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2152957864.025059</v>
+        <v>2157539102.819919</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.52031841</v>
+        <v>12.56009558</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1894926885.15104</v>
+        <v>1891705327.17027</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01976419</v>
+        <v>11.01254651</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13063277</v>
+        <v>5.13600403</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>178798716.3530659</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00707691</v>
+        <v>1.04087521</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.210723</v>
+        <v>0.2109436</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17195711751.3656</v>
+        <v>17177728374.8629</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E801"/>
+  <dimension ref="A1:E809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17513,6 +17513,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="n">
+        <v>2157539102.819919</v>
+      </c>
+      <c r="D802" s="3" t="n">
+        <v>12.56009558</v>
+      </c>
+      <c r="E802" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="n">
+        <v>2418758629.186609</v>
+      </c>
+      <c r="D803" s="3" t="n">
+        <v>14.08078284</v>
+      </c>
+      <c r="E803" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D804" s="3" t="n">
+        <v>5.13600403</v>
+      </c>
+      <c r="E804" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="n">
+        <v>1891705327.17027</v>
+      </c>
+      <c r="D805" s="3" t="n">
+        <v>11.01254651</v>
+      </c>
+      <c r="E805" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="n">
+        <v>3779750876.72166</v>
+      </c>
+      <c r="D806" s="3" t="n">
+        <v>22.00378766</v>
+      </c>
+      <c r="E806" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="n">
+        <v>5832691581.540565</v>
+      </c>
+      <c r="D807" s="3" t="n">
+        <v>33.95496456</v>
+      </c>
+      <c r="E807" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="n">
+        <v>178798716.3530659</v>
+      </c>
+      <c r="D808" s="3" t="n">
+        <v>1.04087521</v>
+      </c>
+      <c r="E808" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D809" s="3" t="n">
+        <v>0.2109436</v>
+      </c>
+      <c r="E809" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5832691581.540565</v>
+        <v>5839296426.046384</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.95496456</v>
+        <v>33.98184752</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3779750876.72166</v>
+        <v>3785946383.75336</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.00378766</v>
+        <v>22.03235516</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2418758629.186609</v>
+        <v>2418013483.318312</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.08078284</v>
+        <v>14.07165513</v>
       </c>
       <c r="E4" t="n">
         <v>302</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2157539102.819919</v>
+        <v>2154007335.660655</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.56009558</v>
+        <v>12.53526855</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1891705327.17027</v>
+        <v>1888539943.880402</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01254651</v>
+        <v>10.99037825</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882252260.5347302</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13600403</v>
+        <v>5.13427639</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>178798716.3530659</v>
+        <v>179284350.3930659</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.04087521</v>
+        <v>1.04334718</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2109436</v>
+        <v>0.21087182</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17177728374.8629</v>
+        <v>17183575502.83978</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E809"/>
+  <dimension ref="A1:E817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17681,6 +17681,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="n">
+        <v>2154007335.660655</v>
+      </c>
+      <c r="D810" s="3" t="n">
+        <v>12.53526855</v>
+      </c>
+      <c r="E810" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="n">
+        <v>2418013483.318312</v>
+      </c>
+      <c r="D811" s="3" t="n">
+        <v>14.07165513</v>
+      </c>
+      <c r="E811" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="n">
+        <v>882252260.5347302</v>
+      </c>
+      <c r="D812" s="3" t="n">
+        <v>5.13427639</v>
+      </c>
+      <c r="E812" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="n">
+        <v>1888539943.880402</v>
+      </c>
+      <c r="D813" s="3" t="n">
+        <v>10.99037825</v>
+      </c>
+      <c r="E813" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="n">
+        <v>3785946383.75336</v>
+      </c>
+      <c r="D814" s="3" t="n">
+        <v>22.03235516</v>
+      </c>
+      <c r="E814" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="n">
+        <v>5839296426.046384</v>
+      </c>
+      <c r="D815" s="3" t="n">
+        <v>33.98184752</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="n">
+        <v>179284350.3930659</v>
+      </c>
+      <c r="D816" s="3" t="n">
+        <v>1.04334718</v>
+      </c>
+      <c r="E816" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D817" s="3" t="n">
+        <v>0.21087182</v>
+      </c>
+      <c r="E817" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5839296426.046384</v>
+        <v>5877742027.789242</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.98184752</v>
+        <v>34.12644749</v>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3785946383.75336</v>
+        <v>3785584524.769129</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.03235516</v>
+        <v>21.97928233</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2418013483.318312</v>
+        <v>2414107835.537634</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.07165513</v>
+        <v>14.01642398</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2154007335.660655</v>
+        <v>2155280640.280155</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.53526855</v>
+        <v>12.51366107</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1888539943.880402</v>
+        <v>1890168004.822285</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99037825</v>
+        <v>10.9744046</v>
       </c>
       <c r="E6" t="n">
         <v>126</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882252260.5347302</v>
+        <v>882249992.2415762</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13427639</v>
+        <v>5.12238507</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>179284350.3930659</v>
+        <v>182053544.9561349</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.04334718</v>
+        <v>1.05701147</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21087182</v>
+        <v>0.21038397</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17183575502.83978</v>
+        <v>17223421889.64903</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E817"/>
+  <dimension ref="A1:E825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17849,6 +17849,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="n">
+        <v>2155280640.280155</v>
+      </c>
+      <c r="D818" s="3" t="n">
+        <v>12.51366107</v>
+      </c>
+      <c r="E818" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="n">
+        <v>2414107835.537634</v>
+      </c>
+      <c r="D819" s="3" t="n">
+        <v>14.01642398</v>
+      </c>
+      <c r="E819" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="n">
+        <v>882249992.2415762</v>
+      </c>
+      <c r="D820" s="3" t="n">
+        <v>5.12238507</v>
+      </c>
+      <c r="E820" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="n">
+        <v>1890168004.822285</v>
+      </c>
+      <c r="D821" s="3" t="n">
+        <v>10.9744046</v>
+      </c>
+      <c r="E821" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="n">
+        <v>3785584524.769129</v>
+      </c>
+      <c r="D822" s="3" t="n">
+        <v>21.97928233</v>
+      </c>
+      <c r="E822" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="n">
+        <v>5877742027.789242</v>
+      </c>
+      <c r="D823" s="3" t="n">
+        <v>34.12644749</v>
+      </c>
+      <c r="E823" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="n">
+        <v>182053544.9561349</v>
+      </c>
+      <c r="D824" s="3" t="n">
+        <v>1.05701147</v>
+      </c>
+      <c r="E824" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D825" s="3" t="n">
+        <v>0.21038397</v>
+      </c>
+      <c r="E825" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5877742027.789242</v>
+        <v>5831276396.098624</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.12644749</v>
+        <v>33.92556323</v>
       </c>
       <c r="E2" t="n">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3785584524.769129</v>
+        <v>3788150010.763194</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.97928233</v>
+        <v>22.03893522</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2414107835.537634</v>
+        <v>2416538989.343521</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.01642398</v>
+        <v>14.05909114</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2155280640.280155</v>
+        <v>2160770914.689443</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.51366107</v>
+        <v>12.57106769</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1890168004.822285</v>
+        <v>1893204983.771802</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.9744046</v>
+        <v>11.01440594</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882249992.2415762</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12238507</v>
+        <v>5.13280218</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>182053544.9561349</v>
+        <v>180018440.6930659</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.05701147</v>
+        <v>1.0473225</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21038397</v>
+        <v>0.2108121</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17223421889.64903</v>
+        <v>17188443876.43046</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E825"/>
+  <dimension ref="A1:E833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18017,6 +18017,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="n">
+        <v>2160770914.689443</v>
+      </c>
+      <c r="D826" s="3" t="n">
+        <v>12.57106769</v>
+      </c>
+      <c r="E826" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="n">
+        <v>2416538989.343521</v>
+      </c>
+      <c r="D827" s="3" t="n">
+        <v>14.05909114</v>
+      </c>
+      <c r="E827" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D828" s="3" t="n">
+        <v>5.13280218</v>
+      </c>
+      <c r="E828" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="n">
+        <v>1893204983.771802</v>
+      </c>
+      <c r="D829" s="3" t="n">
+        <v>11.01440594</v>
+      </c>
+      <c r="E829" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="n">
+        <v>3788150010.763194</v>
+      </c>
+      <c r="D830" s="3" t="n">
+        <v>22.03893522</v>
+      </c>
+      <c r="E830" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="n">
+        <v>5831276396.098624</v>
+      </c>
+      <c r="D831" s="3" t="n">
+        <v>33.92556323</v>
+      </c>
+      <c r="E831" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="n">
+        <v>180018440.6930659</v>
+      </c>
+      <c r="D832" s="3" t="n">
+        <v>1.0473225</v>
+      </c>
+      <c r="E832" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D833" s="3" t="n">
+        <v>0.2108121</v>
+      </c>
+      <c r="E833" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5831276396.098624</v>
+        <v>5846024851.154704</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.92556323</v>
+        <v>33.98276773</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3788150010.763194</v>
+        <v>3791557889.462399</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.03893522</v>
+        <v>22.04021269</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2416538989.343521</v>
+        <v>2417203001.84168</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.05909114</v>
+        <v>14.0511288</v>
       </c>
       <c r="E4" t="n">
         <v>301</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2160770914.689443</v>
+        <v>2162160642.50877</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.57106769</v>
+        <v>12.56857519</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1893204983.771802</v>
+        <v>1894303931.821208</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01440594</v>
+        <v>11.01153214</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882250036.1915761</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.13280218</v>
+        <v>5.12849309</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>180018440.6930659</v>
+        <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.0473225</v>
+        <v>1.00665554</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2108121</v>
+        <v>0.21063483</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17188443876.43046</v>
+        <v>17202909715.44606</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E833"/>
+  <dimension ref="A1:E841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18185,6 +18185,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="n">
+        <v>2162160642.50877</v>
+      </c>
+      <c r="D834" s="3" t="n">
+        <v>12.56857519</v>
+      </c>
+      <c r="E834" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="n">
+        <v>2417203001.84168</v>
+      </c>
+      <c r="D835" s="3" t="n">
+        <v>14.0511288</v>
+      </c>
+      <c r="E835" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="n">
+        <v>882250036.1915761</v>
+      </c>
+      <c r="D836" s="3" t="n">
+        <v>5.12849309</v>
+      </c>
+      <c r="E836" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="n">
+        <v>1894303931.821208</v>
+      </c>
+      <c r="D837" s="3" t="n">
+        <v>11.01153214</v>
+      </c>
+      <c r="E837" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="n">
+        <v>3791557889.462399</v>
+      </c>
+      <c r="D838" s="3" t="n">
+        <v>22.04021269</v>
+      </c>
+      <c r="E838" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="n">
+        <v>5846024851.154704</v>
+      </c>
+      <c r="D839" s="3" t="n">
+        <v>33.98276773</v>
+      </c>
+      <c r="E839" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D840" s="3" t="n">
+        <v>1.00665554</v>
+      </c>
+      <c r="E840" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D841" s="3" t="n">
+        <v>0.21063483</v>
+      </c>
+      <c r="E841" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5846024851.154704</v>
+        <v>5846312098.632238</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.98276773</v>
+        <v>33.95587425</v>
       </c>
       <c r="E2" t="n">
         <v>1221</v>
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3791557889.462399</v>
+        <v>3800623252.408188</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.04021269</v>
+        <v>22.07434072</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2417203001.84168</v>
+        <v>2416593717.949343</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.0511288</v>
+        <v>14.03578034</v>
       </c>
       <c r="E4" t="n">
         <v>301</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2162160642.50877</v>
+        <v>2164060073.517244</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.56857519</v>
+        <v>12.56904361</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1894303931.821208</v>
+        <v>1898133250.981355</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.01153214</v>
+        <v>11.02451817</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882250036.1915761</v>
+        <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12849309</v>
+        <v>5.12417564</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
         <v>173174043.2128489</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00665554</v>
+        <v>1.00580946</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21063483</v>
+        <v>0.21045779</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17202909715.44606</v>
+        <v>17217380577.77203</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E841"/>
+  <dimension ref="A1:E849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18353,6 +18353,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="n">
+        <v>2164060073.517244</v>
+      </c>
+      <c r="D842" s="3" t="n">
+        <v>12.56904361</v>
+      </c>
+      <c r="E842" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="n">
+        <v>2416593717.949343</v>
+      </c>
+      <c r="D843" s="3" t="n">
+        <v>14.03578034</v>
+      </c>
+      <c r="E843" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D844" s="3" t="n">
+        <v>5.12417564</v>
+      </c>
+      <c r="E844" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="n">
+        <v>1898133250.981355</v>
+      </c>
+      <c r="D845" s="3" t="n">
+        <v>11.02451817</v>
+      </c>
+      <c r="E845" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="n">
+        <v>3800623252.408188</v>
+      </c>
+      <c r="D846" s="3" t="n">
+        <v>22.07434072</v>
+      </c>
+      <c r="E846" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="n">
+        <v>5846312098.632238</v>
+      </c>
+      <c r="D847" s="3" t="n">
+        <v>33.95587425</v>
+      </c>
+      <c r="E847" t="n">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="n">
+        <v>173174043.2128489</v>
+      </c>
+      <c r="D848" s="3" t="n">
+        <v>1.00580946</v>
+      </c>
+      <c r="E848" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D849" s="3" t="n">
+        <v>0.21045779</v>
+      </c>
+      <c r="E849" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5846312098.632238</v>
+        <v>5848356601.709789</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.95587425</v>
+        <v>33.94841344</v>
       </c>
       <c r="E2" t="n">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3800623252.408188</v>
+        <v>3802086990.530292</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.07434072</v>
+        <v>22.07027202</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2416593717.949343</v>
+        <v>2416129774.528831</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.03578034</v>
+        <v>14.02509766</v>
       </c>
       <c r="E4" t="n">
         <v>301</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2164060073.517244</v>
+        <v>2165821236.789319</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.56904361</v>
+        <v>12.5721121</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1898133250.981355</v>
+        <v>1900345998.746587</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.02451817</v>
+        <v>11.0310872</v>
       </c>
       <c r="E6" t="n">
         <v>127</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12417564</v>
+        <v>5.12125881</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173174043.2128489</v>
+        <v>175962063.6326069</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.00580946</v>
+        <v>1.02142077</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21045779</v>
+        <v>0.21033799</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17217380577.77203</v>
+        <v>17227186807.00824</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E849"/>
+  <dimension ref="A1:E857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18521,6 +18521,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="n">
+        <v>2165821236.789319</v>
+      </c>
+      <c r="D850" s="3" t="n">
+        <v>12.5721121</v>
+      </c>
+      <c r="E850" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="n">
+        <v>2416129774.528831</v>
+      </c>
+      <c r="D851" s="3" t="n">
+        <v>14.02509766</v>
+      </c>
+      <c r="E851" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D852" s="3" t="n">
+        <v>5.12125881</v>
+      </c>
+      <c r="E852" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="n">
+        <v>1900345998.746587</v>
+      </c>
+      <c r="D853" s="3" t="n">
+        <v>11.0310872</v>
+      </c>
+      <c r="E853" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="n">
+        <v>3802086990.530292</v>
+      </c>
+      <c r="D854" s="3" t="n">
+        <v>22.07027202</v>
+      </c>
+      <c r="E854" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="n">
+        <v>5848356601.709789</v>
+      </c>
+      <c r="D855" s="3" t="n">
+        <v>33.94841344</v>
+      </c>
+      <c r="E855" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="n">
+        <v>175962063.6326069</v>
+      </c>
+      <c r="D856" s="3" t="n">
+        <v>1.02142077</v>
+      </c>
+      <c r="E856" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D857" s="3" t="n">
+        <v>0.21033799</v>
+      </c>
+      <c r="E857" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5848356601.709789</v>
+        <v>5851277529.137275</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.94841344</v>
+        <v>33.93559308</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3802086990.530292</v>
+        <v>3809146066.753886</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.07027202</v>
+        <v>22.0918646</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2416129774.528831</v>
+        <v>2414022203.490965</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.02509766</v>
+        <v>14.00057932</v>
       </c>
       <c r="E4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2165821236.789319</v>
+        <v>2168638365.141737</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.5721121</v>
+        <v>12.57742924</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1900345998.746587</v>
+        <v>1905116500.429217</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.0310872</v>
+        <v>11.04908424</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>882248821.8179371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.12125881</v>
+        <v>5.11676926</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175962063.6326069</v>
+        <v>175617442.8593839</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02142077</v>
+        <v>1.01852665</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21033799</v>
+        <v>0.2101536</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17227186807.00824</v>
+        <v>17242302248.88328</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E857"/>
+  <dimension ref="A1:E865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18689,6 +18689,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="n">
+        <v>2168638365.141737</v>
+      </c>
+      <c r="D858" s="3" t="n">
+        <v>12.57742924</v>
+      </c>
+      <c r="E858" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="n">
+        <v>2414022203.490965</v>
+      </c>
+      <c r="D859" s="3" t="n">
+        <v>14.00057932</v>
+      </c>
+      <c r="E859" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="n">
+        <v>882248821.8179371</v>
+      </c>
+      <c r="D860" s="3" t="n">
+        <v>5.11676926</v>
+      </c>
+      <c r="E860" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="n">
+        <v>1905116500.429217</v>
+      </c>
+      <c r="D861" s="3" t="n">
+        <v>11.04908424</v>
+      </c>
+      <c r="E861" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="n">
+        <v>3809146066.753886</v>
+      </c>
+      <c r="D862" s="3" t="n">
+        <v>22.0918646</v>
+      </c>
+      <c r="E862" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="n">
+        <v>5851277529.137275</v>
+      </c>
+      <c r="D863" s="3" t="n">
+        <v>33.93559308</v>
+      </c>
+      <c r="E863" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="n">
+        <v>175617442.8593839</v>
+      </c>
+      <c r="D864" s="3" t="n">
+        <v>1.01852665</v>
+      </c>
+      <c r="E864" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D865" s="3" t="n">
+        <v>0.2101536</v>
+      </c>
+      <c r="E865" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5851277529.137275</v>
+        <v>5869094270.491745</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.93559308</v>
+        <v>33.99211103</v>
       </c>
       <c r="E2" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3809146066.753886</v>
+        <v>3816427143.670356</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.0918646</v>
+        <v>22.10365164</v>
       </c>
       <c r="E3" t="n">
         <v>232</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2414022203.490965</v>
+        <v>2412502755.531834</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.00057932</v>
+        <v>13.97252417</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2168638365.141737</v>
+        <v>2168557489.472707</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.57742924</v>
+        <v>12.55966314</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1905116500.429217</v>
+        <v>1905215447.770896</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.04908424</v>
+        <v>11.03446155</v>
       </c>
       <c r="E6" t="n">
         <v>128</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882248821.8179371</v>
+        <v>882279210.0173612</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11676926</v>
+        <v>5.10990819</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175617442.8593839</v>
+        <v>175736550.9966199</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01852665</v>
+        <v>1.01781571</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2101536</v>
+        <v>0.20986458</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17242302248.88328</v>
+        <v>17266048187.2044</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E865"/>
+  <dimension ref="A1:E873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18857,6 +18857,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="n">
+        <v>2168557489.472707</v>
+      </c>
+      <c r="D866" s="3" t="n">
+        <v>12.55966314</v>
+      </c>
+      <c r="E866" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="n">
+        <v>2412502755.531834</v>
+      </c>
+      <c r="D867" s="3" t="n">
+        <v>13.97252417</v>
+      </c>
+      <c r="E867" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="n">
+        <v>882279210.0173612</v>
+      </c>
+      <c r="D868" s="3" t="n">
+        <v>5.10990819</v>
+      </c>
+      <c r="E868" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="n">
+        <v>1905215447.770896</v>
+      </c>
+      <c r="D869" s="3" t="n">
+        <v>11.03446155</v>
+      </c>
+      <c r="E869" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="n">
+        <v>3816427143.670356</v>
+      </c>
+      <c r="D870" s="3" t="n">
+        <v>22.10365164</v>
+      </c>
+      <c r="E870" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="n">
+        <v>5869094270.491745</v>
+      </c>
+      <c r="D871" s="3" t="n">
+        <v>33.99211103</v>
+      </c>
+      <c r="E871" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="n">
+        <v>175736550.9966199</v>
+      </c>
+      <c r="D872" s="3" t="n">
+        <v>1.01781571</v>
+      </c>
+      <c r="E872" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D873" s="3" t="n">
+        <v>0.20986458</v>
+      </c>
+      <c r="E873" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5869094270.491745</v>
+        <v>5918468880.587247</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.99211103</v>
+        <v>34.04689339</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3816427143.670356</v>
+        <v>3880704671.252728</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.10365164</v>
+        <v>22.3243445</v>
       </c>
       <c r="E3" t="n">
         <v>232</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2412502755.531834</v>
+        <v>2410832116.990972</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.97252417</v>
+        <v>13.86867883</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2168557489.472707</v>
+        <v>2171719696.727888</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.55966314</v>
+        <v>12.49314822</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1905215447.770896</v>
+        <v>1911619885.811691</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.03446155</v>
+        <v>10.99688446</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882279210.0173612</v>
+        <v>880007867.1828412</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.10990819</v>
+        <v>5.06237925</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175736550.9966199</v>
+        <v>173697645.9574549</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01781571</v>
+        <v>0.99922216</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20986458</v>
+        <v>0.20844919</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17266048187.2044</v>
+        <v>17383286083.76369</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E873"/>
+  <dimension ref="A1:E881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19025,6 +19025,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="n">
+        <v>2171719696.727888</v>
+      </c>
+      <c r="D874" s="3" t="n">
+        <v>12.49314822</v>
+      </c>
+      <c r="E874" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="n">
+        <v>2410832116.990972</v>
+      </c>
+      <c r="D875" s="3" t="n">
+        <v>13.86867883</v>
+      </c>
+      <c r="E875" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="n">
+        <v>880007867.1828412</v>
+      </c>
+      <c r="D876" s="3" t="n">
+        <v>5.06237925</v>
+      </c>
+      <c r="E876" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="n">
+        <v>1911619885.811691</v>
+      </c>
+      <c r="D877" s="3" t="n">
+        <v>10.99688446</v>
+      </c>
+      <c r="E877" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="n">
+        <v>3880704671.252728</v>
+      </c>
+      <c r="D878" s="3" t="n">
+        <v>22.3243445</v>
+      </c>
+      <c r="E878" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="n">
+        <v>5918468880.587247</v>
+      </c>
+      <c r="D879" s="3" t="n">
+        <v>34.04689339</v>
+      </c>
+      <c r="E879" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="n">
+        <v>173697645.9574549</v>
+      </c>
+      <c r="D880" s="3" t="n">
+        <v>0.99922216</v>
+      </c>
+      <c r="E880" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D881" s="3" t="n">
+        <v>0.20844919</v>
+      </c>
+      <c r="E881" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5918468880.587247</v>
+        <v>5919895369.658568</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.04689339</v>
+        <v>34.20397428</v>
       </c>
       <c r="E2" t="n">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3880704671.252728</v>
+        <v>3788437305.973927</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.3243445</v>
+        <v>21.88883486</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2410832116.990972</v>
+        <v>2415924971.297622</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.86867883</v>
+        <v>13.95873245</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2171719696.727888</v>
+        <v>2178668381.598047</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.49314822</v>
+        <v>12.58791121</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1911619885.811691</v>
+        <v>1910279610.710824</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10.99688446</v>
+        <v>11.03721444</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>880007867.1828412</v>
+        <v>882285972.7536422</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.06237925</v>
+        <v>5.09767231</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173697645.9574549</v>
+        <v>175897387.1485879</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.99922216</v>
+        <v>1.01630001</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20844919</v>
+        <v>0.20936044</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17383286083.76369</v>
+        <v>17307624318.3941</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E881"/>
+  <dimension ref="A1:E889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19193,6 +19193,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="n">
+        <v>2178668381.598047</v>
+      </c>
+      <c r="D882" s="3" t="n">
+        <v>12.58791121</v>
+      </c>
+      <c r="E882" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="n">
+        <v>2415924971.297622</v>
+      </c>
+      <c r="D883" s="3" t="n">
+        <v>13.95873245</v>
+      </c>
+      <c r="E883" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="n">
+        <v>882285972.7536422</v>
+      </c>
+      <c r="D884" s="3" t="n">
+        <v>5.09767231</v>
+      </c>
+      <c r="E884" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="n">
+        <v>1910279610.710824</v>
+      </c>
+      <c r="D885" s="3" t="n">
+        <v>11.03721444</v>
+      </c>
+      <c r="E885" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="n">
+        <v>3788437305.973927</v>
+      </c>
+      <c r="D886" s="3" t="n">
+        <v>21.88883486</v>
+      </c>
+      <c r="E886" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="n">
+        <v>5919895369.658568</v>
+      </c>
+      <c r="D887" s="3" t="n">
+        <v>34.20397428</v>
+      </c>
+      <c r="E887" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="n">
+        <v>175897387.1485879</v>
+      </c>
+      <c r="D888" s="3" t="n">
+        <v>1.01630001</v>
+      </c>
+      <c r="E888" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D889" s="3" t="n">
+        <v>0.20936044</v>
+      </c>
+      <c r="E889" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5919895369.658568</v>
+        <v>5826782753.921843</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>34.20397428</v>
+        <v>33.7501381</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3788437305.973927</v>
+        <v>3791479339.876402</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.88883486</v>
+        <v>21.96116738</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2415924971.297622</v>
+        <v>2420558426.264354</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.95873245</v>
+        <v>14.02046114</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2178668381.598047</v>
+        <v>2188335463.719775</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.58791121</v>
+        <v>12.67536945</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1910279610.710824</v>
+        <v>1942504302.863504</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.03721444</v>
+        <v>11.25145578</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882285972.7536422</v>
+        <v>882286032.7536422</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.09767231</v>
+        <v>5.11041457</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175897387.1485879</v>
+        <v>176289208.2936439</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01630001</v>
+        <v>1.02110983</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20936044</v>
+        <v>0.20988375</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17307624318.3941</v>
+        <v>17264470846.94604</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E889"/>
+  <dimension ref="A1:E897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19361,6 +19361,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="n">
+        <v>2188335463.719775</v>
+      </c>
+      <c r="D890" s="3" t="n">
+        <v>12.67536945</v>
+      </c>
+      <c r="E890" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="n">
+        <v>2420558426.264354</v>
+      </c>
+      <c r="D891" s="3" t="n">
+        <v>14.02046114</v>
+      </c>
+      <c r="E891" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="n">
+        <v>882286032.7536422</v>
+      </c>
+      <c r="D892" s="3" t="n">
+        <v>5.11041457</v>
+      </c>
+      <c r="E892" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="n">
+        <v>1942504302.863504</v>
+      </c>
+      <c r="D893" s="3" t="n">
+        <v>11.25145578</v>
+      </c>
+      <c r="E893" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="n">
+        <v>3791479339.876402</v>
+      </c>
+      <c r="D894" s="3" t="n">
+        <v>21.96116738</v>
+      </c>
+      <c r="E894" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="n">
+        <v>5826782753.921843</v>
+      </c>
+      <c r="D895" s="3" t="n">
+        <v>33.7501381</v>
+      </c>
+      <c r="E895" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="n">
+        <v>176289208.2936439</v>
+      </c>
+      <c r="D896" s="3" t="n">
+        <v>1.02110983</v>
+      </c>
+      <c r="E896" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D897" s="3" t="n">
+        <v>0.20988375</v>
+      </c>
+      <c r="E897" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5826782753.921843</v>
+        <v>5844540477.543659</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.7501381</v>
+        <v>33.76310526</v>
       </c>
       <c r="E2" t="n">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3791479339.876402</v>
+        <v>3795180992.890374</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.96116738</v>
+        <v>21.92423782</v>
       </c>
       <c r="E3" t="n">
         <v>231</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2420558426.264354</v>
+        <v>2417169729.630878</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.02046114</v>
+        <v>13.96365657</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2188335463.719775</v>
+        <v>2207615002.093296</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.67536945</v>
+        <v>12.75308777</v>
       </c>
       <c r="E5" t="n">
         <v>48</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1942504302.863504</v>
+        <v>1951499613.499148</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.25145578</v>
+        <v>11.27354445</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882286032.7536422</v>
+        <v>882292458.0671792</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11041457</v>
+        <v>5.096882</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176289208.2936439</v>
+        <v>175901665.4049319</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02110983</v>
+        <v>1.01615969</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20988375</v>
+        <v>0.20932645</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17264470846.94604</v>
+        <v>17310435258.38234</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E897"/>
+  <dimension ref="A1:E905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19529,6 +19529,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="n">
+        <v>2207615002.093296</v>
+      </c>
+      <c r="D898" s="3" t="n">
+        <v>12.75308777</v>
+      </c>
+      <c r="E898" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="n">
+        <v>2417169729.630878</v>
+      </c>
+      <c r="D899" s="3" t="n">
+        <v>13.96365657</v>
+      </c>
+      <c r="E899" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="n">
+        <v>882292458.0671792</v>
+      </c>
+      <c r="D900" s="3" t="n">
+        <v>5.096882</v>
+      </c>
+      <c r="E900" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="n">
+        <v>1951499613.499148</v>
+      </c>
+      <c r="D901" s="3" t="n">
+        <v>11.27354445</v>
+      </c>
+      <c r="E901" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="n">
+        <v>3795180992.890374</v>
+      </c>
+      <c r="D902" s="3" t="n">
+        <v>21.92423782</v>
+      </c>
+      <c r="E902" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="n">
+        <v>5844540477.543659</v>
+      </c>
+      <c r="D903" s="3" t="n">
+        <v>33.76310526</v>
+      </c>
+      <c r="E903" t="n">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="n">
+        <v>175901665.4049319</v>
+      </c>
+      <c r="D904" s="3" t="n">
+        <v>1.01615969</v>
+      </c>
+      <c r="E904" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D905" s="3" t="n">
+        <v>0.20932645</v>
+      </c>
+      <c r="E905" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5844540477.543659</v>
+        <v>5831119164.861821</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.76310526</v>
+        <v>33.82493404</v>
       </c>
       <c r="E2" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3795180992.890374</v>
+        <v>3809952093.536194</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.92423782</v>
+        <v>22.10062504</v>
       </c>
       <c r="E3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2417169729.630878</v>
+        <v>2423254204.79253</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.96365657</v>
+        <v>14.05672073</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2207615002.093296</v>
+        <v>2123374397.793933</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.75308777</v>
+        <v>12.31718936</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1951499613.499148</v>
+        <v>1956718946.96615</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.27354445</v>
+        <v>11.35046077</v>
       </c>
       <c r="E6" t="n">
         <v>130</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882292458.0671792</v>
+        <v>882332554.1704232</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.096882</v>
+        <v>5.11820109</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>175901665.4049319</v>
+        <v>176127986.9406119</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.01615969</v>
+        <v>1.02167652</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.20932645</v>
+        <v>0.21019246</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17310435258.38234</v>
+        <v>17239114668.31454</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E905"/>
+  <dimension ref="A1:E913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19697,6 +19697,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="n">
+        <v>2123374397.793933</v>
+      </c>
+      <c r="D906" s="3" t="n">
+        <v>12.31718936</v>
+      </c>
+      <c r="E906" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="n">
+        <v>2423254204.79253</v>
+      </c>
+      <c r="D907" s="3" t="n">
+        <v>14.05672073</v>
+      </c>
+      <c r="E907" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="n">
+        <v>882332554.1704232</v>
+      </c>
+      <c r="D908" s="3" t="n">
+        <v>5.11820109</v>
+      </c>
+      <c r="E908" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="n">
+        <v>1956718946.96615</v>
+      </c>
+      <c r="D909" s="3" t="n">
+        <v>11.35046077</v>
+      </c>
+      <c r="E909" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="n">
+        <v>3809952093.536194</v>
+      </c>
+      <c r="D910" s="3" t="n">
+        <v>22.10062504</v>
+      </c>
+      <c r="E910" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="n">
+        <v>5831119164.861821</v>
+      </c>
+      <c r="D911" s="3" t="n">
+        <v>33.82493404</v>
+      </c>
+      <c r="E911" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="n">
+        <v>176127986.9406119</v>
+      </c>
+      <c r="D912" s="3" t="n">
+        <v>1.02167652</v>
+      </c>
+      <c r="E912" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D913" s="3" t="n">
+        <v>0.21019246</v>
+      </c>
+      <c r="E913" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/polymarket_30d_topic_share.xlsx
+++ b/docs/data/polymarket_30d_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5831119164.861821</v>
+        <v>5834560211.020885</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>33.82493404</v>
+        <v>33.78566156</v>
       </c>
       <c r="E2" t="n">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3809952093.536194</v>
+        <v>3828412162.409045</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.10062504</v>
+        <v>22.168841</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2423254204.79253</v>
+        <v>2422991616.489436</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.05672073</v>
+        <v>14.03059901</v>
       </c>
       <c r="E4" t="n">
         <v>301</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2123374397.793933</v>
+        <v>2124773860.500342</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.31718936</v>
+        <v>12.30373635</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1956718946.96615</v>
+        <v>1964135248.35792</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11.35046077</v>
+        <v>11.37354083</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>882332554.1704232</v>
+        <v>882347274.6540122</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.11820109</v>
+        <v>5.10932878</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>176127986.9406119</v>
+        <v>175882664.8076469</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.02167652</v>
+        <v>1.01846788</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>36235319.252875</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.21019246</v>
+        <v>0.20982459</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -647,7 +647,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17239114668.31454</v>
+        <v>17269338357.49216</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E913"/>
+  <dimension ref="A1:E921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19865,6 +19865,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="n">
+        <v>2124773860.500342</v>
+      </c>
+      <c r="D914" s="3" t="n">
+        <v>12.30373635</v>
+      </c>
+      <c r="E914" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="n">
+        <v>2422991616.489436</v>
+      </c>
+      <c r="D915" s="3" t="n">
+        <v>14.03059901</v>
+      </c>
+      <c r="E915" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="n">
+        <v>882347274.6540122</v>
+      </c>
+      <c r="D916" s="3" t="n">
+        <v>5.10932878</v>
+      </c>
+      <c r="E916" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="n">
+        <v>1964135248.35792</v>
+      </c>
+      <c r="D917" s="3" t="n">
+        <v>11.37354083</v>
+      </c>
+      <c r="E917" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="n">
+        <v>3828412162.409045</v>
+      </c>
+      <c r="D918" s="3" t="n">
+        <v>22.168841</v>
+      </c>
+      <c r="E918" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="n">
+        <v>5834560211.020885</v>
+      </c>
+      <c r="D919" s="3" t="n">
+        <v>33.78566156</v>
+      </c>
+      <c r="E919" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="n">
+        <v>175882664.8076469</v>
+      </c>
+      <c r="D920" s="3" t="n">
+        <v>1.01846788</v>
+      </c>
+      <c r="E920" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="n">
+        <v>36235319.252875</v>
+      </c>
+      <c r="D921" s="3" t="n">
+        <v>0.20982459</v>
+      </c>
+      <c r="E921" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
